--- a/data/union_join.xlsx
+++ b/data/union_join.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -55,11 +58,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q485"/>
+  <dimension ref="A1:R485"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -512,6 +516,11 @@
       <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>cfaFr</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>date</t>
         </is>
       </c>
     </row>
@@ -557,6 +566,9 @@
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr"/>
       <c r="Q2" t="inlineStr"/>
+      <c r="R2" s="2" t="n">
+        <v>45992</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -600,6 +612,9 @@
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr"/>
       <c r="Q3" t="inlineStr"/>
+      <c r="R3" s="2" t="n">
+        <v>45962</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -643,6 +658,9 @@
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr"/>
       <c r="Q4" t="inlineStr"/>
+      <c r="R4" s="2" t="n">
+        <v>45931</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -686,6 +704,9 @@
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr"/>
       <c r="Q5" t="inlineStr"/>
+      <c r="R5" s="2" t="n">
+        <v>45901</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -729,6 +750,9 @@
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr"/>
       <c r="Q6" t="inlineStr"/>
+      <c r="R6" s="2" t="n">
+        <v>45870</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -772,6 +796,9 @@
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr"/>
       <c r="Q7" t="inlineStr"/>
+      <c r="R7" s="2" t="n">
+        <v>45839</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -815,6 +842,9 @@
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr"/>
       <c r="Q8" t="inlineStr"/>
+      <c r="R8" s="2" t="n">
+        <v>45809</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -858,6 +888,9 @@
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr"/>
       <c r="Q9" t="inlineStr"/>
+      <c r="R9" s="2" t="n">
+        <v>45778</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -901,6 +934,9 @@
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr"/>
       <c r="Q10" t="inlineStr"/>
+      <c r="R10" s="2" t="n">
+        <v>45748</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -944,6 +980,9 @@
       <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr"/>
       <c r="Q11" t="inlineStr"/>
+      <c r="R11" s="2" t="n">
+        <v>45717</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -987,6 +1026,9 @@
       <c r="O12" t="inlineStr"/>
       <c r="P12" t="inlineStr"/>
       <c r="Q12" t="inlineStr"/>
+      <c r="R12" s="2" t="n">
+        <v>45689</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1030,6 +1072,9 @@
       <c r="O13" t="inlineStr"/>
       <c r="P13" t="inlineStr"/>
       <c r="Q13" t="inlineStr"/>
+      <c r="R13" s="2" t="n">
+        <v>45658</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1073,6 +1118,9 @@
       <c r="O14" t="inlineStr"/>
       <c r="P14" t="inlineStr"/>
       <c r="Q14" t="inlineStr"/>
+      <c r="R14" s="2" t="n">
+        <v>45627</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -1116,6 +1164,9 @@
       <c r="O15" t="inlineStr"/>
       <c r="P15" t="inlineStr"/>
       <c r="Q15" t="inlineStr"/>
+      <c r="R15" s="2" t="n">
+        <v>45597</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -1159,6 +1210,9 @@
       <c r="O16" t="inlineStr"/>
       <c r="P16" t="inlineStr"/>
       <c r="Q16" t="inlineStr"/>
+      <c r="R16" s="2" t="n">
+        <v>45566</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -1202,6 +1256,9 @@
       <c r="O17" t="inlineStr"/>
       <c r="P17" t="inlineStr"/>
       <c r="Q17" t="inlineStr"/>
+      <c r="R17" s="2" t="n">
+        <v>45536</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -1245,6 +1302,9 @@
       <c r="O18" t="inlineStr"/>
       <c r="P18" t="inlineStr"/>
       <c r="Q18" t="inlineStr"/>
+      <c r="R18" s="2" t="n">
+        <v>45505</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -1288,6 +1348,9 @@
       <c r="O19" t="inlineStr"/>
       <c r="P19" t="inlineStr"/>
       <c r="Q19" t="inlineStr"/>
+      <c r="R19" s="2" t="n">
+        <v>45474</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -1331,6 +1394,9 @@
       <c r="O20" t="inlineStr"/>
       <c r="P20" t="inlineStr"/>
       <c r="Q20" t="inlineStr"/>
+      <c r="R20" s="2" t="n">
+        <v>45444</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -1374,6 +1440,9 @@
       <c r="O21" t="inlineStr"/>
       <c r="P21" t="inlineStr"/>
       <c r="Q21" t="inlineStr"/>
+      <c r="R21" s="2" t="n">
+        <v>45413</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -1417,6 +1486,9 @@
       <c r="O22" t="inlineStr"/>
       <c r="P22" t="inlineStr"/>
       <c r="Q22" t="inlineStr"/>
+      <c r="R22" s="2" t="n">
+        <v>45383</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -1460,6 +1532,9 @@
       <c r="O23" t="inlineStr"/>
       <c r="P23" t="inlineStr"/>
       <c r="Q23" t="inlineStr"/>
+      <c r="R23" s="2" t="n">
+        <v>45352</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -1503,6 +1578,9 @@
       <c r="O24" t="inlineStr"/>
       <c r="P24" t="inlineStr"/>
       <c r="Q24" t="inlineStr"/>
+      <c r="R24" s="2" t="n">
+        <v>45323</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -1546,6 +1624,9 @@
       <c r="O25" t="inlineStr"/>
       <c r="P25" t="inlineStr"/>
       <c r="Q25" t="inlineStr"/>
+      <c r="R25" s="2" t="n">
+        <v>45292</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -1589,6 +1670,9 @@
       <c r="O26" t="inlineStr"/>
       <c r="P26" t="inlineStr"/>
       <c r="Q26" t="inlineStr"/>
+      <c r="R26" s="2" t="n">
+        <v>45261</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -1632,6 +1716,9 @@
       <c r="O27" t="inlineStr"/>
       <c r="P27" t="inlineStr"/>
       <c r="Q27" t="inlineStr"/>
+      <c r="R27" s="2" t="n">
+        <v>45231</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -1675,6 +1762,9 @@
       <c r="O28" t="inlineStr"/>
       <c r="P28" t="inlineStr"/>
       <c r="Q28" t="inlineStr"/>
+      <c r="R28" s="2" t="n">
+        <v>45200</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -1718,6 +1808,9 @@
       <c r="O29" t="inlineStr"/>
       <c r="P29" t="inlineStr"/>
       <c r="Q29" t="inlineStr"/>
+      <c r="R29" s="2" t="n">
+        <v>45170</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -1761,6 +1854,9 @@
       <c r="O30" t="inlineStr"/>
       <c r="P30" t="inlineStr"/>
       <c r="Q30" t="inlineStr"/>
+      <c r="R30" s="2" t="n">
+        <v>45139</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -1804,6 +1900,9 @@
       <c r="O31" t="inlineStr"/>
       <c r="P31" t="inlineStr"/>
       <c r="Q31" t="inlineStr"/>
+      <c r="R31" s="2" t="n">
+        <v>45108</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -1847,6 +1946,9 @@
       <c r="O32" t="inlineStr"/>
       <c r="P32" t="inlineStr"/>
       <c r="Q32" t="inlineStr"/>
+      <c r="R32" s="2" t="n">
+        <v>45078</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -1890,6 +1992,9 @@
       <c r="O33" t="inlineStr"/>
       <c r="P33" t="inlineStr"/>
       <c r="Q33" t="inlineStr"/>
+      <c r="R33" s="2" t="n">
+        <v>45047</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -1933,6 +2038,9 @@
       <c r="O34" t="inlineStr"/>
       <c r="P34" t="inlineStr"/>
       <c r="Q34" t="inlineStr"/>
+      <c r="R34" s="2" t="n">
+        <v>45017</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -1976,6 +2084,9 @@
       <c r="O35" t="inlineStr"/>
       <c r="P35" t="inlineStr"/>
       <c r="Q35" t="inlineStr"/>
+      <c r="R35" s="2" t="n">
+        <v>44986</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -2019,6 +2130,9 @@
       <c r="O36" t="inlineStr"/>
       <c r="P36" t="inlineStr"/>
       <c r="Q36" t="inlineStr"/>
+      <c r="R36" s="2" t="n">
+        <v>44958</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -2062,6 +2176,9 @@
       <c r="O37" t="inlineStr"/>
       <c r="P37" t="inlineStr"/>
       <c r="Q37" t="inlineStr"/>
+      <c r="R37" s="2" t="n">
+        <v>44927</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -2105,6 +2222,9 @@
       <c r="O38" t="inlineStr"/>
       <c r="P38" t="inlineStr"/>
       <c r="Q38" t="inlineStr"/>
+      <c r="R38" s="2" t="n">
+        <v>44896</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -2148,6 +2268,9 @@
       <c r="O39" t="inlineStr"/>
       <c r="P39" t="inlineStr"/>
       <c r="Q39" t="inlineStr"/>
+      <c r="R39" s="2" t="n">
+        <v>44866</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -2191,6 +2314,9 @@
       <c r="O40" t="inlineStr"/>
       <c r="P40" t="inlineStr"/>
       <c r="Q40" t="inlineStr"/>
+      <c r="R40" s="2" t="n">
+        <v>44835</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -2234,6 +2360,9 @@
       <c r="O41" t="inlineStr"/>
       <c r="P41" t="inlineStr"/>
       <c r="Q41" t="inlineStr"/>
+      <c r="R41" s="2" t="n">
+        <v>44805</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -2277,6 +2406,9 @@
       <c r="O42" t="inlineStr"/>
       <c r="P42" t="inlineStr"/>
       <c r="Q42" t="inlineStr"/>
+      <c r="R42" s="2" t="n">
+        <v>44774</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -2320,6 +2452,9 @@
       <c r="O43" t="inlineStr"/>
       <c r="P43" t="inlineStr"/>
       <c r="Q43" t="inlineStr"/>
+      <c r="R43" s="2" t="n">
+        <v>44743</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -2363,6 +2498,9 @@
       <c r="O44" t="inlineStr"/>
       <c r="P44" t="inlineStr"/>
       <c r="Q44" t="inlineStr"/>
+      <c r="R44" s="2" t="n">
+        <v>44713</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -2406,6 +2544,9 @@
       <c r="O45" t="inlineStr"/>
       <c r="P45" t="inlineStr"/>
       <c r="Q45" t="inlineStr"/>
+      <c r="R45" s="2" t="n">
+        <v>44682</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -2449,6 +2590,9 @@
       <c r="O46" t="inlineStr"/>
       <c r="P46" t="inlineStr"/>
       <c r="Q46" t="inlineStr"/>
+      <c r="R46" s="2" t="n">
+        <v>44652</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -2492,6 +2636,9 @@
       <c r="O47" t="inlineStr"/>
       <c r="P47" t="inlineStr"/>
       <c r="Q47" t="inlineStr"/>
+      <c r="R47" s="2" t="n">
+        <v>44621</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -2535,6 +2682,9 @@
       <c r="O48" t="inlineStr"/>
       <c r="P48" t="inlineStr"/>
       <c r="Q48" t="inlineStr"/>
+      <c r="R48" s="2" t="n">
+        <v>44593</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -2578,6 +2728,9 @@
       <c r="O49" t="inlineStr"/>
       <c r="P49" t="inlineStr"/>
       <c r="Q49" t="inlineStr"/>
+      <c r="R49" s="2" t="n">
+        <v>44562</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -2621,6 +2774,9 @@
       <c r="O50" t="inlineStr"/>
       <c r="P50" t="inlineStr"/>
       <c r="Q50" t="inlineStr"/>
+      <c r="R50" s="2" t="n">
+        <v>44531</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -2664,6 +2820,9 @@
       <c r="O51" t="inlineStr"/>
       <c r="P51" t="inlineStr"/>
       <c r="Q51" t="inlineStr"/>
+      <c r="R51" s="2" t="n">
+        <v>44501</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -2707,6 +2866,9 @@
       <c r="O52" t="inlineStr"/>
       <c r="P52" t="inlineStr"/>
       <c r="Q52" t="inlineStr"/>
+      <c r="R52" s="2" t="n">
+        <v>44470</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -2750,6 +2912,9 @@
       <c r="O53" t="inlineStr"/>
       <c r="P53" t="inlineStr"/>
       <c r="Q53" t="inlineStr"/>
+      <c r="R53" s="2" t="n">
+        <v>44440</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -2793,6 +2958,9 @@
       <c r="O54" t="inlineStr"/>
       <c r="P54" t="inlineStr"/>
       <c r="Q54" t="inlineStr"/>
+      <c r="R54" s="2" t="n">
+        <v>44409</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -2836,6 +3004,9 @@
       <c r="O55" t="inlineStr"/>
       <c r="P55" t="inlineStr"/>
       <c r="Q55" t="inlineStr"/>
+      <c r="R55" s="2" t="n">
+        <v>44378</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -2879,6 +3050,9 @@
       <c r="O56" t="inlineStr"/>
       <c r="P56" t="inlineStr"/>
       <c r="Q56" t="inlineStr"/>
+      <c r="R56" s="2" t="n">
+        <v>44348</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -2922,6 +3096,9 @@
       <c r="O57" t="inlineStr"/>
       <c r="P57" t="inlineStr"/>
       <c r="Q57" t="inlineStr"/>
+      <c r="R57" s="2" t="n">
+        <v>44317</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -2965,6 +3142,9 @@
       <c r="O58" t="inlineStr"/>
       <c r="P58" t="inlineStr"/>
       <c r="Q58" t="inlineStr"/>
+      <c r="R58" s="2" t="n">
+        <v>44287</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -3008,6 +3188,9 @@
       <c r="O59" t="inlineStr"/>
       <c r="P59" t="inlineStr"/>
       <c r="Q59" t="inlineStr"/>
+      <c r="R59" s="2" t="n">
+        <v>44256</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -3051,6 +3234,9 @@
       <c r="O60" t="inlineStr"/>
       <c r="P60" t="inlineStr"/>
       <c r="Q60" t="inlineStr"/>
+      <c r="R60" s="2" t="n">
+        <v>44228</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -3094,6 +3280,9 @@
       <c r="O61" t="inlineStr"/>
       <c r="P61" t="inlineStr"/>
       <c r="Q61" t="inlineStr"/>
+      <c r="R61" s="2" t="n">
+        <v>44197</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -3137,6 +3326,9 @@
       <c r="O62" t="inlineStr"/>
       <c r="P62" t="inlineStr"/>
       <c r="Q62" t="inlineStr"/>
+      <c r="R62" s="2" t="n">
+        <v>44166</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -3180,6 +3372,9 @@
       <c r="O63" t="inlineStr"/>
       <c r="P63" t="inlineStr"/>
       <c r="Q63" t="inlineStr"/>
+      <c r="R63" s="2" t="n">
+        <v>44136</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -3223,6 +3418,9 @@
       <c r="O64" t="inlineStr"/>
       <c r="P64" t="inlineStr"/>
       <c r="Q64" t="inlineStr"/>
+      <c r="R64" s="2" t="n">
+        <v>44105</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -3266,6 +3464,9 @@
       <c r="O65" t="inlineStr"/>
       <c r="P65" t="inlineStr"/>
       <c r="Q65" t="inlineStr"/>
+      <c r="R65" s="2" t="n">
+        <v>44075</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -3309,6 +3510,9 @@
       <c r="O66" t="inlineStr"/>
       <c r="P66" t="inlineStr"/>
       <c r="Q66" t="inlineStr"/>
+      <c r="R66" s="2" t="n">
+        <v>44044</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -3352,6 +3556,9 @@
       <c r="O67" t="inlineStr"/>
       <c r="P67" t="inlineStr"/>
       <c r="Q67" t="inlineStr"/>
+      <c r="R67" s="2" t="n">
+        <v>44013</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -3395,6 +3602,9 @@
       <c r="O68" t="inlineStr"/>
       <c r="P68" t="inlineStr"/>
       <c r="Q68" t="inlineStr"/>
+      <c r="R68" s="2" t="n">
+        <v>43983</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -3438,6 +3648,9 @@
       <c r="O69" t="inlineStr"/>
       <c r="P69" t="inlineStr"/>
       <c r="Q69" t="inlineStr"/>
+      <c r="R69" s="2" t="n">
+        <v>43952</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -3481,6 +3694,9 @@
       <c r="O70" t="inlineStr"/>
       <c r="P70" t="inlineStr"/>
       <c r="Q70" t="inlineStr"/>
+      <c r="R70" s="2" t="n">
+        <v>43922</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -3524,6 +3740,9 @@
       <c r="O71" t="inlineStr"/>
       <c r="P71" t="inlineStr"/>
       <c r="Q71" t="inlineStr"/>
+      <c r="R71" s="2" t="n">
+        <v>43891</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -3567,6 +3786,9 @@
       <c r="O72" t="inlineStr"/>
       <c r="P72" t="inlineStr"/>
       <c r="Q72" t="inlineStr"/>
+      <c r="R72" s="2" t="n">
+        <v>43862</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -3610,6 +3832,9 @@
       <c r="O73" t="inlineStr"/>
       <c r="P73" t="inlineStr"/>
       <c r="Q73" t="inlineStr"/>
+      <c r="R73" s="2" t="n">
+        <v>43831</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -3653,6 +3878,9 @@
       <c r="O74" t="inlineStr"/>
       <c r="P74" t="inlineStr"/>
       <c r="Q74" t="inlineStr"/>
+      <c r="R74" s="2" t="n">
+        <v>43800</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -3696,6 +3924,9 @@
       <c r="O75" t="inlineStr"/>
       <c r="P75" t="inlineStr"/>
       <c r="Q75" t="inlineStr"/>
+      <c r="R75" s="2" t="n">
+        <v>43770</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -3739,6 +3970,9 @@
       <c r="O76" t="inlineStr"/>
       <c r="P76" t="inlineStr"/>
       <c r="Q76" t="inlineStr"/>
+      <c r="R76" s="2" t="n">
+        <v>43739</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -3782,6 +4016,9 @@
       <c r="O77" t="inlineStr"/>
       <c r="P77" t="inlineStr"/>
       <c r="Q77" t="inlineStr"/>
+      <c r="R77" s="2" t="n">
+        <v>43709</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -3825,6 +4062,9 @@
       <c r="O78" t="inlineStr"/>
       <c r="P78" t="inlineStr"/>
       <c r="Q78" t="inlineStr"/>
+      <c r="R78" s="2" t="n">
+        <v>43678</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -3868,6 +4108,9 @@
       <c r="O79" t="inlineStr"/>
       <c r="P79" t="inlineStr"/>
       <c r="Q79" t="inlineStr"/>
+      <c r="R79" s="2" t="n">
+        <v>43647</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -3911,6 +4154,9 @@
       <c r="O80" t="inlineStr"/>
       <c r="P80" t="inlineStr"/>
       <c r="Q80" t="inlineStr"/>
+      <c r="R80" s="2" t="n">
+        <v>43617</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -3954,6 +4200,9 @@
       <c r="O81" t="inlineStr"/>
       <c r="P81" t="inlineStr"/>
       <c r="Q81" t="inlineStr"/>
+      <c r="R81" s="2" t="n">
+        <v>43586</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -3997,6 +4246,9 @@
       <c r="O82" t="inlineStr"/>
       <c r="P82" t="inlineStr"/>
       <c r="Q82" t="inlineStr"/>
+      <c r="R82" s="2" t="n">
+        <v>43556</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -4040,6 +4292,9 @@
       <c r="O83" t="inlineStr"/>
       <c r="P83" t="inlineStr"/>
       <c r="Q83" t="inlineStr"/>
+      <c r="R83" s="2" t="n">
+        <v>43525</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -4083,6 +4338,9 @@
       <c r="O84" t="inlineStr"/>
       <c r="P84" t="inlineStr"/>
       <c r="Q84" t="inlineStr"/>
+      <c r="R84" s="2" t="n">
+        <v>43497</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -4126,6 +4384,9 @@
       <c r="O85" t="inlineStr"/>
       <c r="P85" t="inlineStr"/>
       <c r="Q85" t="inlineStr"/>
+      <c r="R85" s="2" t="n">
+        <v>43466</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -4169,6 +4430,9 @@
       <c r="O86" t="inlineStr"/>
       <c r="P86" t="inlineStr"/>
       <c r="Q86" t="inlineStr"/>
+      <c r="R86" s="2" t="n">
+        <v>43435</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -4212,6 +4476,9 @@
       <c r="O87" t="inlineStr"/>
       <c r="P87" t="inlineStr"/>
       <c r="Q87" t="inlineStr"/>
+      <c r="R87" s="2" t="n">
+        <v>43405</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -4255,6 +4522,9 @@
       <c r="O88" t="inlineStr"/>
       <c r="P88" t="inlineStr"/>
       <c r="Q88" t="inlineStr"/>
+      <c r="R88" s="2" t="n">
+        <v>43374</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -4298,6 +4568,9 @@
       <c r="O89" t="inlineStr"/>
       <c r="P89" t="inlineStr"/>
       <c r="Q89" t="inlineStr"/>
+      <c r="R89" s="2" t="n">
+        <v>43344</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -4341,6 +4614,9 @@
       <c r="O90" t="inlineStr"/>
       <c r="P90" t="inlineStr"/>
       <c r="Q90" t="inlineStr"/>
+      <c r="R90" s="2" t="n">
+        <v>43313</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -4384,6 +4660,9 @@
       <c r="O91" t="inlineStr"/>
       <c r="P91" t="inlineStr"/>
       <c r="Q91" t="inlineStr"/>
+      <c r="R91" s="2" t="n">
+        <v>43282</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -4427,6 +4706,9 @@
       <c r="O92" t="inlineStr"/>
       <c r="P92" t="inlineStr"/>
       <c r="Q92" t="inlineStr"/>
+      <c r="R92" s="2" t="n">
+        <v>43252</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -4470,6 +4752,9 @@
       <c r="O93" t="inlineStr"/>
       <c r="P93" t="inlineStr"/>
       <c r="Q93" t="inlineStr"/>
+      <c r="R93" s="2" t="n">
+        <v>43221</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -4513,6 +4798,9 @@
       <c r="O94" t="inlineStr"/>
       <c r="P94" t="inlineStr"/>
       <c r="Q94" t="inlineStr"/>
+      <c r="R94" s="2" t="n">
+        <v>43191</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -4556,6 +4844,9 @@
       <c r="O95" t="inlineStr"/>
       <c r="P95" t="inlineStr"/>
       <c r="Q95" t="inlineStr"/>
+      <c r="R95" s="2" t="n">
+        <v>43160</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -4599,6 +4890,9 @@
       <c r="O96" t="inlineStr"/>
       <c r="P96" t="inlineStr"/>
       <c r="Q96" t="inlineStr"/>
+      <c r="R96" s="2" t="n">
+        <v>43132</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -4642,6 +4936,9 @@
       <c r="O97" t="inlineStr"/>
       <c r="P97" t="inlineStr"/>
       <c r="Q97" t="inlineStr"/>
+      <c r="R97" s="2" t="n">
+        <v>43101</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -4685,6 +4982,9 @@
       <c r="O98" t="inlineStr"/>
       <c r="P98" t="inlineStr"/>
       <c r="Q98" t="inlineStr"/>
+      <c r="R98" s="2" t="n">
+        <v>43070</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -4728,6 +5028,9 @@
       <c r="O99" t="inlineStr"/>
       <c r="P99" t="inlineStr"/>
       <c r="Q99" t="inlineStr"/>
+      <c r="R99" s="2" t="n">
+        <v>43040</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -4771,6 +5074,9 @@
       <c r="O100" t="inlineStr"/>
       <c r="P100" t="inlineStr"/>
       <c r="Q100" t="inlineStr"/>
+      <c r="R100" s="2" t="n">
+        <v>43009</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -4814,6 +5120,9 @@
       <c r="O101" t="inlineStr"/>
       <c r="P101" t="inlineStr"/>
       <c r="Q101" t="inlineStr"/>
+      <c r="R101" s="2" t="n">
+        <v>42979</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -4857,6 +5166,9 @@
       <c r="O102" t="inlineStr"/>
       <c r="P102" t="inlineStr"/>
       <c r="Q102" t="inlineStr"/>
+      <c r="R102" s="2" t="n">
+        <v>42948</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -4900,6 +5212,9 @@
       <c r="O103" t="inlineStr"/>
       <c r="P103" t="inlineStr"/>
       <c r="Q103" t="inlineStr"/>
+      <c r="R103" s="2" t="n">
+        <v>42917</v>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -4943,6 +5258,9 @@
       <c r="O104" t="inlineStr"/>
       <c r="P104" t="inlineStr"/>
       <c r="Q104" t="inlineStr"/>
+      <c r="R104" s="2" t="n">
+        <v>42887</v>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -4986,6 +5304,9 @@
       <c r="O105" t="inlineStr"/>
       <c r="P105" t="inlineStr"/>
       <c r="Q105" t="inlineStr"/>
+      <c r="R105" s="2" t="n">
+        <v>42856</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -5029,6 +5350,9 @@
       <c r="O106" t="inlineStr"/>
       <c r="P106" t="inlineStr"/>
       <c r="Q106" t="inlineStr"/>
+      <c r="R106" s="2" t="n">
+        <v>42826</v>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -5072,6 +5396,9 @@
       <c r="O107" t="inlineStr"/>
       <c r="P107" t="inlineStr"/>
       <c r="Q107" t="inlineStr"/>
+      <c r="R107" s="2" t="n">
+        <v>42795</v>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -5115,6 +5442,9 @@
       <c r="O108" t="inlineStr"/>
       <c r="P108" t="inlineStr"/>
       <c r="Q108" t="inlineStr"/>
+      <c r="R108" s="2" t="n">
+        <v>42767</v>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -5158,6 +5488,9 @@
       <c r="O109" t="inlineStr"/>
       <c r="P109" t="inlineStr"/>
       <c r="Q109" t="inlineStr"/>
+      <c r="R109" s="2" t="n">
+        <v>42736</v>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -5201,6 +5534,9 @@
       <c r="O110" t="inlineStr"/>
       <c r="P110" t="inlineStr"/>
       <c r="Q110" t="inlineStr"/>
+      <c r="R110" s="2" t="n">
+        <v>42705</v>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -5244,6 +5580,9 @@
       <c r="O111" t="inlineStr"/>
       <c r="P111" t="inlineStr"/>
       <c r="Q111" t="inlineStr"/>
+      <c r="R111" s="2" t="n">
+        <v>42675</v>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -5287,6 +5626,9 @@
       <c r="O112" t="inlineStr"/>
       <c r="P112" t="inlineStr"/>
       <c r="Q112" t="inlineStr"/>
+      <c r="R112" s="2" t="n">
+        <v>42644</v>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -5330,6 +5672,9 @@
       <c r="O113" t="inlineStr"/>
       <c r="P113" t="inlineStr"/>
       <c r="Q113" t="inlineStr"/>
+      <c r="R113" s="2" t="n">
+        <v>42614</v>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -5373,6 +5718,9 @@
       <c r="O114" t="inlineStr"/>
       <c r="P114" t="inlineStr"/>
       <c r="Q114" t="inlineStr"/>
+      <c r="R114" s="2" t="n">
+        <v>42583</v>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -5416,6 +5764,9 @@
       <c r="O115" t="inlineStr"/>
       <c r="P115" t="inlineStr"/>
       <c r="Q115" t="inlineStr"/>
+      <c r="R115" s="2" t="n">
+        <v>42552</v>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -5459,6 +5810,9 @@
       <c r="O116" t="inlineStr"/>
       <c r="P116" t="inlineStr"/>
       <c r="Q116" t="inlineStr"/>
+      <c r="R116" s="2" t="n">
+        <v>42522</v>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -5502,6 +5856,9 @@
       <c r="O117" t="inlineStr"/>
       <c r="P117" t="inlineStr"/>
       <c r="Q117" t="inlineStr"/>
+      <c r="R117" s="2" t="n">
+        <v>42491</v>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -5545,6 +5902,9 @@
       <c r="O118" t="inlineStr"/>
       <c r="P118" t="inlineStr"/>
       <c r="Q118" t="inlineStr"/>
+      <c r="R118" s="2" t="n">
+        <v>42461</v>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -5588,6 +5948,9 @@
       <c r="O119" t="inlineStr"/>
       <c r="P119" t="inlineStr"/>
       <c r="Q119" t="inlineStr"/>
+      <c r="R119" s="2" t="n">
+        <v>42430</v>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -5631,6 +5994,9 @@
       <c r="O120" t="inlineStr"/>
       <c r="P120" t="inlineStr"/>
       <c r="Q120" t="inlineStr"/>
+      <c r="R120" s="2" t="n">
+        <v>42401</v>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -5674,6 +6040,9 @@
       <c r="O121" t="inlineStr"/>
       <c r="P121" t="inlineStr"/>
       <c r="Q121" t="inlineStr"/>
+      <c r="R121" s="2" t="n">
+        <v>42370</v>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -5717,6 +6086,9 @@
       <c r="O122" t="inlineStr"/>
       <c r="P122" t="inlineStr"/>
       <c r="Q122" t="inlineStr"/>
+      <c r="R122" s="2" t="n">
+        <v>42339</v>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -5760,6 +6132,9 @@
       <c r="O123" t="inlineStr"/>
       <c r="P123" t="inlineStr"/>
       <c r="Q123" t="inlineStr"/>
+      <c r="R123" s="2" t="n">
+        <v>42309</v>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -5803,6 +6178,9 @@
       <c r="O124" t="inlineStr"/>
       <c r="P124" t="inlineStr"/>
       <c r="Q124" t="inlineStr"/>
+      <c r="R124" s="2" t="n">
+        <v>42278</v>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -5846,6 +6224,9 @@
       <c r="O125" t="inlineStr"/>
       <c r="P125" t="inlineStr"/>
       <c r="Q125" t="inlineStr"/>
+      <c r="R125" s="2" t="n">
+        <v>42248</v>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -5889,6 +6270,9 @@
       <c r="O126" t="inlineStr"/>
       <c r="P126" t="inlineStr"/>
       <c r="Q126" t="inlineStr"/>
+      <c r="R126" s="2" t="n">
+        <v>42217</v>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -5932,6 +6316,9 @@
       <c r="O127" t="inlineStr"/>
       <c r="P127" t="inlineStr"/>
       <c r="Q127" t="inlineStr"/>
+      <c r="R127" s="2" t="n">
+        <v>42186</v>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -5975,6 +6362,9 @@
       <c r="O128" t="inlineStr"/>
       <c r="P128" t="inlineStr"/>
       <c r="Q128" t="inlineStr"/>
+      <c r="R128" s="2" t="n">
+        <v>42156</v>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -6018,6 +6408,9 @@
       <c r="O129" t="inlineStr"/>
       <c r="P129" t="inlineStr"/>
       <c r="Q129" t="inlineStr"/>
+      <c r="R129" s="2" t="n">
+        <v>42125</v>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -6061,6 +6454,9 @@
       <c r="O130" t="inlineStr"/>
       <c r="P130" t="inlineStr"/>
       <c r="Q130" t="inlineStr"/>
+      <c r="R130" s="2" t="n">
+        <v>42095</v>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -6104,6 +6500,9 @@
       <c r="O131" t="inlineStr"/>
       <c r="P131" t="inlineStr"/>
       <c r="Q131" t="inlineStr"/>
+      <c r="R131" s="2" t="n">
+        <v>42064</v>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -6147,6 +6546,9 @@
       <c r="O132" t="inlineStr"/>
       <c r="P132" t="inlineStr"/>
       <c r="Q132" t="inlineStr"/>
+      <c r="R132" s="2" t="n">
+        <v>42036</v>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -6190,6 +6592,9 @@
       <c r="O133" t="inlineStr"/>
       <c r="P133" t="inlineStr"/>
       <c r="Q133" t="inlineStr"/>
+      <c r="R133" s="2" t="n">
+        <v>42005</v>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -6233,6 +6638,9 @@
       <c r="O134" t="inlineStr"/>
       <c r="P134" t="inlineStr"/>
       <c r="Q134" t="inlineStr"/>
+      <c r="R134" s="2" t="n">
+        <v>41974</v>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -6276,6 +6684,9 @@
       <c r="O135" t="inlineStr"/>
       <c r="P135" t="inlineStr"/>
       <c r="Q135" t="inlineStr"/>
+      <c r="R135" s="2" t="n">
+        <v>41944</v>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -6319,6 +6730,9 @@
       <c r="O136" t="inlineStr"/>
       <c r="P136" t="inlineStr"/>
       <c r="Q136" t="inlineStr"/>
+      <c r="R136" s="2" t="n">
+        <v>41913</v>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -6362,6 +6776,9 @@
       <c r="O137" t="inlineStr"/>
       <c r="P137" t="inlineStr"/>
       <c r="Q137" t="inlineStr"/>
+      <c r="R137" s="2" t="n">
+        <v>41883</v>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -6405,6 +6822,9 @@
       <c r="O138" t="inlineStr"/>
       <c r="P138" t="inlineStr"/>
       <c r="Q138" t="inlineStr"/>
+      <c r="R138" s="2" t="n">
+        <v>41852</v>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -6448,6 +6868,9 @@
       <c r="O139" t="inlineStr"/>
       <c r="P139" t="inlineStr"/>
       <c r="Q139" t="inlineStr"/>
+      <c r="R139" s="2" t="n">
+        <v>41821</v>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -6491,6 +6914,9 @@
       <c r="O140" t="inlineStr"/>
       <c r="P140" t="inlineStr"/>
       <c r="Q140" t="inlineStr"/>
+      <c r="R140" s="2" t="n">
+        <v>41791</v>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -6534,6 +6960,9 @@
       <c r="O141" t="inlineStr"/>
       <c r="P141" t="inlineStr"/>
       <c r="Q141" t="inlineStr"/>
+      <c r="R141" s="2" t="n">
+        <v>41760</v>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -6577,6 +7006,9 @@
       <c r="O142" t="inlineStr"/>
       <c r="P142" t="inlineStr"/>
       <c r="Q142" t="inlineStr"/>
+      <c r="R142" s="2" t="n">
+        <v>41730</v>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
@@ -6620,6 +7052,9 @@
       <c r="O143" t="inlineStr"/>
       <c r="P143" t="inlineStr"/>
       <c r="Q143" t="inlineStr"/>
+      <c r="R143" s="2" t="n">
+        <v>41699</v>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
@@ -6663,6 +7098,9 @@
       <c r="O144" t="inlineStr"/>
       <c r="P144" t="inlineStr"/>
       <c r="Q144" t="inlineStr"/>
+      <c r="R144" s="2" t="n">
+        <v>41671</v>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
@@ -6706,6 +7144,9 @@
       <c r="O145" t="inlineStr"/>
       <c r="P145" t="inlineStr"/>
       <c r="Q145" t="inlineStr"/>
+      <c r="R145" s="2" t="n">
+        <v>41640</v>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
@@ -6749,6 +7190,9 @@
       <c r="O146" t="inlineStr"/>
       <c r="P146" t="inlineStr"/>
       <c r="Q146" t="inlineStr"/>
+      <c r="R146" s="2" t="n">
+        <v>41609</v>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
@@ -6792,6 +7236,9 @@
       <c r="O147" t="inlineStr"/>
       <c r="P147" t="inlineStr"/>
       <c r="Q147" t="inlineStr"/>
+      <c r="R147" s="2" t="n">
+        <v>41579</v>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
@@ -6835,6 +7282,9 @@
       <c r="O148" t="inlineStr"/>
       <c r="P148" t="inlineStr"/>
       <c r="Q148" t="inlineStr"/>
+      <c r="R148" s="2" t="n">
+        <v>41548</v>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
@@ -6878,6 +7328,9 @@
       <c r="O149" t="inlineStr"/>
       <c r="P149" t="inlineStr"/>
       <c r="Q149" t="inlineStr"/>
+      <c r="R149" s="2" t="n">
+        <v>41518</v>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
@@ -6921,6 +7374,9 @@
       <c r="O150" t="inlineStr"/>
       <c r="P150" t="inlineStr"/>
       <c r="Q150" t="inlineStr"/>
+      <c r="R150" s="2" t="n">
+        <v>41487</v>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
@@ -6964,6 +7420,9 @@
       <c r="O151" t="inlineStr"/>
       <c r="P151" t="inlineStr"/>
       <c r="Q151" t="inlineStr"/>
+      <c r="R151" s="2" t="n">
+        <v>41456</v>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
@@ -7007,6 +7466,9 @@
       <c r="O152" t="inlineStr"/>
       <c r="P152" t="inlineStr"/>
       <c r="Q152" t="inlineStr"/>
+      <c r="R152" s="2" t="n">
+        <v>41426</v>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
@@ -7050,6 +7512,9 @@
       <c r="O153" t="inlineStr"/>
       <c r="P153" t="inlineStr"/>
       <c r="Q153" t="inlineStr"/>
+      <c r="R153" s="2" t="n">
+        <v>41395</v>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
@@ -7093,6 +7558,9 @@
       <c r="O154" t="inlineStr"/>
       <c r="P154" t="inlineStr"/>
       <c r="Q154" t="inlineStr"/>
+      <c r="R154" s="2" t="n">
+        <v>41365</v>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
@@ -7136,6 +7604,9 @@
       <c r="O155" t="inlineStr"/>
       <c r="P155" t="inlineStr"/>
       <c r="Q155" t="inlineStr"/>
+      <c r="R155" s="2" t="n">
+        <v>41334</v>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
@@ -7179,6 +7650,9 @@
       <c r="O156" t="inlineStr"/>
       <c r="P156" t="inlineStr"/>
       <c r="Q156" t="inlineStr"/>
+      <c r="R156" s="2" t="n">
+        <v>41306</v>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
@@ -7222,6 +7696,9 @@
       <c r="O157" t="inlineStr"/>
       <c r="P157" t="inlineStr"/>
       <c r="Q157" t="inlineStr"/>
+      <c r="R157" s="2" t="n">
+        <v>41275</v>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
@@ -7265,6 +7742,9 @@
       <c r="O158" t="inlineStr"/>
       <c r="P158" t="inlineStr"/>
       <c r="Q158" t="inlineStr"/>
+      <c r="R158" s="2" t="n">
+        <v>41244</v>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
@@ -7308,6 +7788,9 @@
       <c r="O159" t="inlineStr"/>
       <c r="P159" t="inlineStr"/>
       <c r="Q159" t="inlineStr"/>
+      <c r="R159" s="2" t="n">
+        <v>41214</v>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
@@ -7351,6 +7834,9 @@
       <c r="O160" t="inlineStr"/>
       <c r="P160" t="inlineStr"/>
       <c r="Q160" t="inlineStr"/>
+      <c r="R160" s="2" t="n">
+        <v>41183</v>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
@@ -7394,6 +7880,9 @@
       <c r="O161" t="inlineStr"/>
       <c r="P161" t="inlineStr"/>
       <c r="Q161" t="inlineStr"/>
+      <c r="R161" s="2" t="n">
+        <v>41153</v>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
@@ -7437,6 +7926,9 @@
       <c r="O162" t="inlineStr"/>
       <c r="P162" t="inlineStr"/>
       <c r="Q162" t="inlineStr"/>
+      <c r="R162" s="2" t="n">
+        <v>41122</v>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
@@ -7480,6 +7972,9 @@
       <c r="O163" t="inlineStr"/>
       <c r="P163" t="inlineStr"/>
       <c r="Q163" t="inlineStr"/>
+      <c r="R163" s="2" t="n">
+        <v>41091</v>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
@@ -7523,6 +8018,9 @@
       <c r="O164" t="inlineStr"/>
       <c r="P164" t="inlineStr"/>
       <c r="Q164" t="inlineStr"/>
+      <c r="R164" s="2" t="n">
+        <v>41061</v>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
@@ -7566,6 +8064,9 @@
       <c r="O165" t="inlineStr"/>
       <c r="P165" t="inlineStr"/>
       <c r="Q165" t="inlineStr"/>
+      <c r="R165" s="2" t="n">
+        <v>41030</v>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
@@ -7609,6 +8110,9 @@
       <c r="O166" t="inlineStr"/>
       <c r="P166" t="inlineStr"/>
       <c r="Q166" t="inlineStr"/>
+      <c r="R166" s="2" t="n">
+        <v>41000</v>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
@@ -7652,6 +8156,9 @@
       <c r="O167" t="inlineStr"/>
       <c r="P167" t="inlineStr"/>
       <c r="Q167" t="inlineStr"/>
+      <c r="R167" s="2" t="n">
+        <v>40969</v>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
@@ -7695,6 +8202,9 @@
       <c r="O168" t="inlineStr"/>
       <c r="P168" t="inlineStr"/>
       <c r="Q168" t="inlineStr"/>
+      <c r="R168" s="2" t="n">
+        <v>40940</v>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
@@ -7738,6 +8248,9 @@
       <c r="O169" t="inlineStr"/>
       <c r="P169" t="inlineStr"/>
       <c r="Q169" t="inlineStr"/>
+      <c r="R169" s="2" t="n">
+        <v>40909</v>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
@@ -7781,6 +8294,9 @@
       <c r="O170" t="inlineStr"/>
       <c r="P170" t="inlineStr"/>
       <c r="Q170" t="inlineStr"/>
+      <c r="R170" s="2" t="n">
+        <v>40878</v>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
@@ -7824,6 +8340,9 @@
       <c r="O171" t="inlineStr"/>
       <c r="P171" t="inlineStr"/>
       <c r="Q171" t="inlineStr"/>
+      <c r="R171" s="2" t="n">
+        <v>40848</v>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
@@ -7867,6 +8386,9 @@
       <c r="O172" t="inlineStr"/>
       <c r="P172" t="inlineStr"/>
       <c r="Q172" t="inlineStr"/>
+      <c r="R172" s="2" t="n">
+        <v>40817</v>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
@@ -7910,6 +8432,9 @@
       <c r="O173" t="inlineStr"/>
       <c r="P173" t="inlineStr"/>
       <c r="Q173" t="inlineStr"/>
+      <c r="R173" s="2" t="n">
+        <v>40787</v>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="n">
@@ -7953,6 +8478,9 @@
       <c r="O174" t="inlineStr"/>
       <c r="P174" t="inlineStr"/>
       <c r="Q174" t="inlineStr"/>
+      <c r="R174" s="2" t="n">
+        <v>40756</v>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
@@ -7996,6 +8524,9 @@
       <c r="O175" t="inlineStr"/>
       <c r="P175" t="inlineStr"/>
       <c r="Q175" t="inlineStr"/>
+      <c r="R175" s="2" t="n">
+        <v>40725</v>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
@@ -8039,6 +8570,9 @@
       <c r="O176" t="inlineStr"/>
       <c r="P176" t="inlineStr"/>
       <c r="Q176" t="inlineStr"/>
+      <c r="R176" s="2" t="n">
+        <v>40695</v>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
@@ -8082,6 +8616,9 @@
       <c r="O177" t="inlineStr"/>
       <c r="P177" t="inlineStr"/>
       <c r="Q177" t="inlineStr"/>
+      <c r="R177" s="2" t="n">
+        <v>40664</v>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
@@ -8125,6 +8662,9 @@
       <c r="O178" t="inlineStr"/>
       <c r="P178" t="inlineStr"/>
       <c r="Q178" t="inlineStr"/>
+      <c r="R178" s="2" t="n">
+        <v>40634</v>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="n">
@@ -8168,6 +8708,9 @@
       <c r="O179" t="inlineStr"/>
       <c r="P179" t="inlineStr"/>
       <c r="Q179" t="inlineStr"/>
+      <c r="R179" s="2" t="n">
+        <v>40603</v>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="n">
@@ -8211,6 +8754,9 @@
       <c r="O180" t="inlineStr"/>
       <c r="P180" t="inlineStr"/>
       <c r="Q180" t="inlineStr"/>
+      <c r="R180" s="2" t="n">
+        <v>40575</v>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="n">
@@ -8254,6 +8800,9 @@
       <c r="O181" t="inlineStr"/>
       <c r="P181" t="inlineStr"/>
       <c r="Q181" t="inlineStr"/>
+      <c r="R181" s="2" t="n">
+        <v>40544</v>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="n">
@@ -8297,6 +8846,9 @@
       <c r="O182" t="inlineStr"/>
       <c r="P182" t="inlineStr"/>
       <c r="Q182" t="inlineStr"/>
+      <c r="R182" s="2" t="n">
+        <v>40513</v>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="n">
@@ -8340,6 +8892,9 @@
       <c r="O183" t="inlineStr"/>
       <c r="P183" t="inlineStr"/>
       <c r="Q183" t="inlineStr"/>
+      <c r="R183" s="2" t="n">
+        <v>40483</v>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="n">
@@ -8383,6 +8938,9 @@
       <c r="O184" t="inlineStr"/>
       <c r="P184" t="inlineStr"/>
       <c r="Q184" t="inlineStr"/>
+      <c r="R184" s="2" t="n">
+        <v>40452</v>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="n">
@@ -8426,6 +8984,9 @@
       <c r="O185" t="inlineStr"/>
       <c r="P185" t="inlineStr"/>
       <c r="Q185" t="inlineStr"/>
+      <c r="R185" s="2" t="n">
+        <v>40422</v>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="n">
@@ -8469,6 +9030,9 @@
       <c r="O186" t="inlineStr"/>
       <c r="P186" t="inlineStr"/>
       <c r="Q186" t="inlineStr"/>
+      <c r="R186" s="2" t="n">
+        <v>40391</v>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="n">
@@ -8512,6 +9076,9 @@
       <c r="O187" t="inlineStr"/>
       <c r="P187" t="inlineStr"/>
       <c r="Q187" t="inlineStr"/>
+      <c r="R187" s="2" t="n">
+        <v>40360</v>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="n">
@@ -8555,6 +9122,9 @@
       <c r="O188" t="inlineStr"/>
       <c r="P188" t="inlineStr"/>
       <c r="Q188" t="inlineStr"/>
+      <c r="R188" s="2" t="n">
+        <v>40330</v>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="n">
@@ -8598,6 +9168,9 @@
       <c r="O189" t="inlineStr"/>
       <c r="P189" t="inlineStr"/>
       <c r="Q189" t="inlineStr"/>
+      <c r="R189" s="2" t="n">
+        <v>40299</v>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="n">
@@ -8641,6 +9214,9 @@
       <c r="O190" t="inlineStr"/>
       <c r="P190" t="inlineStr"/>
       <c r="Q190" t="inlineStr"/>
+      <c r="R190" s="2" t="n">
+        <v>40269</v>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="n">
@@ -8684,6 +9260,9 @@
       <c r="O191" t="inlineStr"/>
       <c r="P191" t="inlineStr"/>
       <c r="Q191" t="inlineStr"/>
+      <c r="R191" s="2" t="n">
+        <v>40238</v>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="n">
@@ -8727,6 +9306,9 @@
       <c r="O192" t="inlineStr"/>
       <c r="P192" t="inlineStr"/>
       <c r="Q192" t="inlineStr"/>
+      <c r="R192" s="2" t="n">
+        <v>40210</v>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="n">
@@ -8770,6 +9352,9 @@
       <c r="O193" t="inlineStr"/>
       <c r="P193" t="inlineStr"/>
       <c r="Q193" t="inlineStr"/>
+      <c r="R193" s="2" t="n">
+        <v>40179</v>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="n">
@@ -8813,6 +9398,9 @@
       <c r="O194" t="inlineStr"/>
       <c r="P194" t="inlineStr"/>
       <c r="Q194" t="inlineStr"/>
+      <c r="R194" s="2" t="n">
+        <v>40148</v>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="n">
@@ -8856,6 +9444,9 @@
       <c r="O195" t="inlineStr"/>
       <c r="P195" t="inlineStr"/>
       <c r="Q195" t="inlineStr"/>
+      <c r="R195" s="2" t="n">
+        <v>40118</v>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="n">
@@ -8899,6 +9490,9 @@
       <c r="O196" t="inlineStr"/>
       <c r="P196" t="inlineStr"/>
       <c r="Q196" t="inlineStr"/>
+      <c r="R196" s="2" t="n">
+        <v>40087</v>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="n">
@@ -8942,6 +9536,9 @@
       <c r="O197" t="inlineStr"/>
       <c r="P197" t="inlineStr"/>
       <c r="Q197" t="inlineStr"/>
+      <c r="R197" s="2" t="n">
+        <v>40057</v>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="n">
@@ -8985,6 +9582,9 @@
       <c r="O198" t="inlineStr"/>
       <c r="P198" t="inlineStr"/>
       <c r="Q198" t="inlineStr"/>
+      <c r="R198" s="2" t="n">
+        <v>40026</v>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="n">
@@ -9028,6 +9628,9 @@
       <c r="O199" t="inlineStr"/>
       <c r="P199" t="inlineStr"/>
       <c r="Q199" t="inlineStr"/>
+      <c r="R199" s="2" t="n">
+        <v>39995</v>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="n">
@@ -9071,6 +9674,9 @@
       <c r="O200" t="inlineStr"/>
       <c r="P200" t="inlineStr"/>
       <c r="Q200" t="inlineStr"/>
+      <c r="R200" s="2" t="n">
+        <v>39965</v>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="n">
@@ -9114,6 +9720,9 @@
       <c r="O201" t="inlineStr"/>
       <c r="P201" t="inlineStr"/>
       <c r="Q201" t="inlineStr"/>
+      <c r="R201" s="2" t="n">
+        <v>39934</v>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="n">
@@ -9157,6 +9766,9 @@
       <c r="O202" t="inlineStr"/>
       <c r="P202" t="inlineStr"/>
       <c r="Q202" t="inlineStr"/>
+      <c r="R202" s="2" t="n">
+        <v>39904</v>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="n">
@@ -9200,6 +9812,9 @@
       <c r="O203" t="inlineStr"/>
       <c r="P203" t="inlineStr"/>
       <c r="Q203" t="inlineStr"/>
+      <c r="R203" s="2" t="n">
+        <v>39873</v>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="n">
@@ -9243,6 +9858,9 @@
       <c r="O204" t="inlineStr"/>
       <c r="P204" t="inlineStr"/>
       <c r="Q204" t="inlineStr"/>
+      <c r="R204" s="2" t="n">
+        <v>39845</v>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="n">
@@ -9286,6 +9904,9 @@
       <c r="O205" t="inlineStr"/>
       <c r="P205" t="inlineStr"/>
       <c r="Q205" t="inlineStr"/>
+      <c r="R205" s="2" t="n">
+        <v>39814</v>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="n">
@@ -9329,6 +9950,9 @@
       <c r="O206" t="inlineStr"/>
       <c r="P206" t="inlineStr"/>
       <c r="Q206" t="inlineStr"/>
+      <c r="R206" s="2" t="n">
+        <v>39783</v>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="n">
@@ -9372,6 +9996,9 @@
       <c r="O207" t="inlineStr"/>
       <c r="P207" t="inlineStr"/>
       <c r="Q207" t="inlineStr"/>
+      <c r="R207" s="2" t="n">
+        <v>39753</v>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="n">
@@ -9415,6 +10042,9 @@
       <c r="O208" t="inlineStr"/>
       <c r="P208" t="inlineStr"/>
       <c r="Q208" t="inlineStr"/>
+      <c r="R208" s="2" t="n">
+        <v>39722</v>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="n">
@@ -9458,6 +10088,9 @@
       <c r="O209" t="inlineStr"/>
       <c r="P209" t="inlineStr"/>
       <c r="Q209" t="inlineStr"/>
+      <c r="R209" s="2" t="n">
+        <v>39692</v>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="n">
@@ -9501,6 +10134,9 @@
       <c r="O210" t="inlineStr"/>
       <c r="P210" t="inlineStr"/>
       <c r="Q210" t="inlineStr"/>
+      <c r="R210" s="2" t="n">
+        <v>39661</v>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="n">
@@ -9544,6 +10180,9 @@
       <c r="O211" t="inlineStr"/>
       <c r="P211" t="inlineStr"/>
       <c r="Q211" t="inlineStr"/>
+      <c r="R211" s="2" t="n">
+        <v>39630</v>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="n">
@@ -9587,6 +10226,9 @@
       <c r="O212" t="inlineStr"/>
       <c r="P212" t="inlineStr"/>
       <c r="Q212" t="inlineStr"/>
+      <c r="R212" s="2" t="n">
+        <v>39600</v>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="n">
@@ -9630,6 +10272,9 @@
       <c r="O213" t="inlineStr"/>
       <c r="P213" t="inlineStr"/>
       <c r="Q213" t="inlineStr"/>
+      <c r="R213" s="2" t="n">
+        <v>39569</v>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="n">
@@ -9673,6 +10318,9 @@
       <c r="O214" t="inlineStr"/>
       <c r="P214" t="inlineStr"/>
       <c r="Q214" t="inlineStr"/>
+      <c r="R214" s="2" t="n">
+        <v>39539</v>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="n">
@@ -9716,6 +10364,9 @@
       <c r="O215" t="inlineStr"/>
       <c r="P215" t="inlineStr"/>
       <c r="Q215" t="inlineStr"/>
+      <c r="R215" s="2" t="n">
+        <v>39508</v>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="n">
@@ -9759,6 +10410,9 @@
       <c r="O216" t="inlineStr"/>
       <c r="P216" t="inlineStr"/>
       <c r="Q216" t="inlineStr"/>
+      <c r="R216" s="2" t="n">
+        <v>39479</v>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="n">
@@ -9802,6 +10456,9 @@
       <c r="O217" t="inlineStr"/>
       <c r="P217" t="inlineStr"/>
       <c r="Q217" t="inlineStr"/>
+      <c r="R217" s="2" t="n">
+        <v>39448</v>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="n">
@@ -9845,6 +10502,9 @@
       <c r="O218" t="inlineStr"/>
       <c r="P218" t="inlineStr"/>
       <c r="Q218" t="inlineStr"/>
+      <c r="R218" s="2" t="n">
+        <v>39417</v>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="n">
@@ -9888,6 +10548,9 @@
       <c r="O219" t="inlineStr"/>
       <c r="P219" t="inlineStr"/>
       <c r="Q219" t="inlineStr"/>
+      <c r="R219" s="2" t="n">
+        <v>39387</v>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="n">
@@ -9931,6 +10594,9 @@
       <c r="O220" t="inlineStr"/>
       <c r="P220" t="inlineStr"/>
       <c r="Q220" t="inlineStr"/>
+      <c r="R220" s="2" t="n">
+        <v>39356</v>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="n">
@@ -9974,6 +10640,9 @@
       <c r="O221" t="inlineStr"/>
       <c r="P221" t="inlineStr"/>
       <c r="Q221" t="inlineStr"/>
+      <c r="R221" s="2" t="n">
+        <v>39326</v>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="n">
@@ -10017,6 +10686,9 @@
       <c r="O222" t="inlineStr"/>
       <c r="P222" t="inlineStr"/>
       <c r="Q222" t="inlineStr"/>
+      <c r="R222" s="2" t="n">
+        <v>39295</v>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="n">
@@ -10060,6 +10732,9 @@
       <c r="O223" t="inlineStr"/>
       <c r="P223" t="inlineStr"/>
       <c r="Q223" t="inlineStr"/>
+      <c r="R223" s="2" t="n">
+        <v>39264</v>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="n">
@@ -10103,6 +10778,9 @@
       <c r="O224" t="inlineStr"/>
       <c r="P224" t="inlineStr"/>
       <c r="Q224" t="inlineStr"/>
+      <c r="R224" s="2" t="n">
+        <v>39234</v>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="n">
@@ -10146,6 +10824,9 @@
       <c r="O225" t="inlineStr"/>
       <c r="P225" t="inlineStr"/>
       <c r="Q225" t="inlineStr"/>
+      <c r="R225" s="2" t="n">
+        <v>39203</v>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="n">
@@ -10189,6 +10870,9 @@
       <c r="O226" t="inlineStr"/>
       <c r="P226" t="inlineStr"/>
       <c r="Q226" t="inlineStr"/>
+      <c r="R226" s="2" t="n">
+        <v>39173</v>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="n">
@@ -10232,6 +10916,9 @@
       <c r="O227" t="inlineStr"/>
       <c r="P227" t="inlineStr"/>
       <c r="Q227" t="inlineStr"/>
+      <c r="R227" s="2" t="n">
+        <v>39142</v>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="n">
@@ -10275,6 +10962,9 @@
       <c r="O228" t="inlineStr"/>
       <c r="P228" t="inlineStr"/>
       <c r="Q228" t="inlineStr"/>
+      <c r="R228" s="2" t="n">
+        <v>39114</v>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="n">
@@ -10318,6 +11008,9 @@
       <c r="O229" t="inlineStr"/>
       <c r="P229" t="inlineStr"/>
       <c r="Q229" t="inlineStr"/>
+      <c r="R229" s="2" t="n">
+        <v>39083</v>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="n">
@@ -10361,6 +11054,9 @@
       <c r="O230" t="inlineStr"/>
       <c r="P230" t="inlineStr"/>
       <c r="Q230" t="inlineStr"/>
+      <c r="R230" s="2" t="n">
+        <v>39052</v>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="n">
@@ -10404,6 +11100,9 @@
       <c r="O231" t="inlineStr"/>
       <c r="P231" t="inlineStr"/>
       <c r="Q231" t="inlineStr"/>
+      <c r="R231" s="2" t="n">
+        <v>39022</v>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="n">
@@ -10447,6 +11146,9 @@
       <c r="O232" t="inlineStr"/>
       <c r="P232" t="inlineStr"/>
       <c r="Q232" t="inlineStr"/>
+      <c r="R232" s="2" t="n">
+        <v>38991</v>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="n">
@@ -10490,6 +11192,9 @@
       <c r="O233" t="inlineStr"/>
       <c r="P233" t="inlineStr"/>
       <c r="Q233" t="inlineStr"/>
+      <c r="R233" s="2" t="n">
+        <v>38961</v>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="n">
@@ -10533,6 +11238,9 @@
       <c r="O234" t="inlineStr"/>
       <c r="P234" t="inlineStr"/>
       <c r="Q234" t="inlineStr"/>
+      <c r="R234" s="2" t="n">
+        <v>38930</v>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="n">
@@ -10576,6 +11284,9 @@
       <c r="O235" t="inlineStr"/>
       <c r="P235" t="inlineStr"/>
       <c r="Q235" t="inlineStr"/>
+      <c r="R235" s="2" t="n">
+        <v>38899</v>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="n">
@@ -10619,6 +11330,9 @@
       <c r="O236" t="inlineStr"/>
       <c r="P236" t="inlineStr"/>
       <c r="Q236" t="inlineStr"/>
+      <c r="R236" s="2" t="n">
+        <v>38869</v>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="n">
@@ -10662,6 +11376,9 @@
       <c r="O237" t="inlineStr"/>
       <c r="P237" t="inlineStr"/>
       <c r="Q237" t="inlineStr"/>
+      <c r="R237" s="2" t="n">
+        <v>38838</v>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="n">
@@ -10705,6 +11422,9 @@
       <c r="O238" t="inlineStr"/>
       <c r="P238" t="inlineStr"/>
       <c r="Q238" t="inlineStr"/>
+      <c r="R238" s="2" t="n">
+        <v>38808</v>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="n">
@@ -10748,6 +11468,9 @@
       <c r="O239" t="inlineStr"/>
       <c r="P239" t="inlineStr"/>
       <c r="Q239" t="inlineStr"/>
+      <c r="R239" s="2" t="n">
+        <v>38777</v>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="n">
@@ -10791,6 +11514,9 @@
       <c r="O240" t="inlineStr"/>
       <c r="P240" t="inlineStr"/>
       <c r="Q240" t="inlineStr"/>
+      <c r="R240" s="2" t="n">
+        <v>38749</v>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="n">
@@ -10834,6 +11560,9 @@
       <c r="O241" t="inlineStr"/>
       <c r="P241" t="inlineStr"/>
       <c r="Q241" t="inlineStr"/>
+      <c r="R241" s="2" t="n">
+        <v>38718</v>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="n">
@@ -10877,6 +11606,9 @@
       <c r="O242" t="inlineStr"/>
       <c r="P242" t="inlineStr"/>
       <c r="Q242" t="inlineStr"/>
+      <c r="R242" s="2" t="n">
+        <v>38687</v>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="n">
@@ -10920,6 +11652,9 @@
       <c r="O243" t="inlineStr"/>
       <c r="P243" t="inlineStr"/>
       <c r="Q243" t="inlineStr"/>
+      <c r="R243" s="2" t="n">
+        <v>38657</v>
+      </c>
     </row>
     <row r="244">
       <c r="A244" t="n">
@@ -10963,6 +11698,9 @@
       <c r="O244" t="inlineStr"/>
       <c r="P244" t="inlineStr"/>
       <c r="Q244" t="inlineStr"/>
+      <c r="R244" s="2" t="n">
+        <v>38626</v>
+      </c>
     </row>
     <row r="245">
       <c r="A245" t="n">
@@ -11006,6 +11744,9 @@
       <c r="O245" t="inlineStr"/>
       <c r="P245" t="inlineStr"/>
       <c r="Q245" t="inlineStr"/>
+      <c r="R245" s="2" t="n">
+        <v>38596</v>
+      </c>
     </row>
     <row r="246">
       <c r="A246" t="n">
@@ -11049,6 +11790,9 @@
       <c r="O246" t="inlineStr"/>
       <c r="P246" t="inlineStr"/>
       <c r="Q246" t="inlineStr"/>
+      <c r="R246" s="2" t="n">
+        <v>38565</v>
+      </c>
     </row>
     <row r="247">
       <c r="A247" t="n">
@@ -11092,6 +11836,9 @@
       <c r="O247" t="inlineStr"/>
       <c r="P247" t="inlineStr"/>
       <c r="Q247" t="inlineStr"/>
+      <c r="R247" s="2" t="n">
+        <v>38534</v>
+      </c>
     </row>
     <row r="248">
       <c r="A248" t="n">
@@ -11135,6 +11882,9 @@
       <c r="O248" t="inlineStr"/>
       <c r="P248" t="inlineStr"/>
       <c r="Q248" t="inlineStr"/>
+      <c r="R248" s="2" t="n">
+        <v>38504</v>
+      </c>
     </row>
     <row r="249">
       <c r="A249" t="n">
@@ -11178,6 +11928,9 @@
       <c r="O249" t="inlineStr"/>
       <c r="P249" t="inlineStr"/>
       <c r="Q249" t="inlineStr"/>
+      <c r="R249" s="2" t="n">
+        <v>38473</v>
+      </c>
     </row>
     <row r="250">
       <c r="A250" t="n">
@@ -11221,6 +11974,9 @@
       <c r="O250" t="inlineStr"/>
       <c r="P250" t="inlineStr"/>
       <c r="Q250" t="inlineStr"/>
+      <c r="R250" s="2" t="n">
+        <v>38443</v>
+      </c>
     </row>
     <row r="251">
       <c r="A251" t="n">
@@ -11264,6 +12020,9 @@
       <c r="O251" t="inlineStr"/>
       <c r="P251" t="inlineStr"/>
       <c r="Q251" t="inlineStr"/>
+      <c r="R251" s="2" t="n">
+        <v>38412</v>
+      </c>
     </row>
     <row r="252">
       <c r="A252" t="n">
@@ -11307,6 +12066,9 @@
       <c r="O252" t="inlineStr"/>
       <c r="P252" t="inlineStr"/>
       <c r="Q252" t="inlineStr"/>
+      <c r="R252" s="2" t="n">
+        <v>38384</v>
+      </c>
     </row>
     <row r="253">
       <c r="A253" t="n">
@@ -11350,6 +12112,9 @@
       <c r="O253" t="inlineStr"/>
       <c r="P253" t="inlineStr"/>
       <c r="Q253" t="inlineStr"/>
+      <c r="R253" s="2" t="n">
+        <v>38353</v>
+      </c>
     </row>
     <row r="254">
       <c r="A254" t="n">
@@ -11393,6 +12158,9 @@
       <c r="O254" t="inlineStr"/>
       <c r="P254" t="inlineStr"/>
       <c r="Q254" t="inlineStr"/>
+      <c r="R254" s="2" t="n">
+        <v>38322</v>
+      </c>
     </row>
     <row r="255">
       <c r="A255" t="n">
@@ -11436,6 +12204,9 @@
       <c r="O255" t="inlineStr"/>
       <c r="P255" t="inlineStr"/>
       <c r="Q255" t="inlineStr"/>
+      <c r="R255" s="2" t="n">
+        <v>38292</v>
+      </c>
     </row>
     <row r="256">
       <c r="A256" t="n">
@@ -11479,6 +12250,9 @@
       <c r="O256" t="inlineStr"/>
       <c r="P256" t="inlineStr"/>
       <c r="Q256" t="inlineStr"/>
+      <c r="R256" s="2" t="n">
+        <v>38261</v>
+      </c>
     </row>
     <row r="257">
       <c r="A257" t="n">
@@ -11522,6 +12296,9 @@
       <c r="O257" t="inlineStr"/>
       <c r="P257" t="inlineStr"/>
       <c r="Q257" t="inlineStr"/>
+      <c r="R257" s="2" t="n">
+        <v>38231</v>
+      </c>
     </row>
     <row r="258">
       <c r="A258" t="n">
@@ -11565,6 +12342,9 @@
       <c r="O258" t="inlineStr"/>
       <c r="P258" t="inlineStr"/>
       <c r="Q258" t="inlineStr"/>
+      <c r="R258" s="2" t="n">
+        <v>38200</v>
+      </c>
     </row>
     <row r="259">
       <c r="A259" t="n">
@@ -11608,6 +12388,9 @@
       <c r="O259" t="inlineStr"/>
       <c r="P259" t="inlineStr"/>
       <c r="Q259" t="inlineStr"/>
+      <c r="R259" s="2" t="n">
+        <v>38169</v>
+      </c>
     </row>
     <row r="260">
       <c r="A260" t="n">
@@ -11651,6 +12434,9 @@
       <c r="O260" t="inlineStr"/>
       <c r="P260" t="inlineStr"/>
       <c r="Q260" t="inlineStr"/>
+      <c r="R260" s="2" t="n">
+        <v>38139</v>
+      </c>
     </row>
     <row r="261">
       <c r="A261" t="n">
@@ -11694,6 +12480,9 @@
       <c r="O261" t="inlineStr"/>
       <c r="P261" t="inlineStr"/>
       <c r="Q261" t="inlineStr"/>
+      <c r="R261" s="2" t="n">
+        <v>38108</v>
+      </c>
     </row>
     <row r="262">
       <c r="A262" t="n">
@@ -11737,6 +12526,9 @@
       <c r="O262" t="inlineStr"/>
       <c r="P262" t="inlineStr"/>
       <c r="Q262" t="inlineStr"/>
+      <c r="R262" s="2" t="n">
+        <v>38078</v>
+      </c>
     </row>
     <row r="263">
       <c r="A263" t="n">
@@ -11780,6 +12572,9 @@
       <c r="O263" t="inlineStr"/>
       <c r="P263" t="inlineStr"/>
       <c r="Q263" t="inlineStr"/>
+      <c r="R263" s="2" t="n">
+        <v>38047</v>
+      </c>
     </row>
     <row r="264">
       <c r="A264" t="n">
@@ -11823,6 +12618,9 @@
       <c r="O264" t="inlineStr"/>
       <c r="P264" t="inlineStr"/>
       <c r="Q264" t="inlineStr"/>
+      <c r="R264" s="2" t="n">
+        <v>38018</v>
+      </c>
     </row>
     <row r="265">
       <c r="A265" t="n">
@@ -11866,6 +12664,9 @@
       <c r="O265" t="inlineStr"/>
       <c r="P265" t="inlineStr"/>
       <c r="Q265" t="inlineStr"/>
+      <c r="R265" s="2" t="n">
+        <v>37987</v>
+      </c>
     </row>
     <row r="266">
       <c r="A266" t="n">
@@ -11909,6 +12710,9 @@
       <c r="O266" t="inlineStr"/>
       <c r="P266" t="inlineStr"/>
       <c r="Q266" t="inlineStr"/>
+      <c r="R266" s="2" t="n">
+        <v>37956</v>
+      </c>
     </row>
     <row r="267">
       <c r="A267" t="n">
@@ -11952,6 +12756,9 @@
       <c r="O267" t="inlineStr"/>
       <c r="P267" t="inlineStr"/>
       <c r="Q267" t="inlineStr"/>
+      <c r="R267" s="2" t="n">
+        <v>37926</v>
+      </c>
     </row>
     <row r="268">
       <c r="A268" t="n">
@@ -11995,6 +12802,9 @@
       <c r="O268" t="inlineStr"/>
       <c r="P268" t="inlineStr"/>
       <c r="Q268" t="inlineStr"/>
+      <c r="R268" s="2" t="n">
+        <v>37895</v>
+      </c>
     </row>
     <row r="269">
       <c r="A269" t="n">
@@ -12038,6 +12848,9 @@
       <c r="O269" t="inlineStr"/>
       <c r="P269" t="inlineStr"/>
       <c r="Q269" t="inlineStr"/>
+      <c r="R269" s="2" t="n">
+        <v>37865</v>
+      </c>
     </row>
     <row r="270">
       <c r="A270" t="n">
@@ -12081,6 +12894,9 @@
       <c r="O270" t="inlineStr"/>
       <c r="P270" t="inlineStr"/>
       <c r="Q270" t="inlineStr"/>
+      <c r="R270" s="2" t="n">
+        <v>37834</v>
+      </c>
     </row>
     <row r="271">
       <c r="A271" t="n">
@@ -12124,6 +12940,9 @@
       <c r="O271" t="inlineStr"/>
       <c r="P271" t="inlineStr"/>
       <c r="Q271" t="inlineStr"/>
+      <c r="R271" s="2" t="n">
+        <v>37803</v>
+      </c>
     </row>
     <row r="272">
       <c r="A272" t="n">
@@ -12167,6 +12986,9 @@
       <c r="O272" t="inlineStr"/>
       <c r="P272" t="inlineStr"/>
       <c r="Q272" t="inlineStr"/>
+      <c r="R272" s="2" t="n">
+        <v>37773</v>
+      </c>
     </row>
     <row r="273">
       <c r="A273" t="n">
@@ -12210,6 +13032,9 @@
       <c r="O273" t="inlineStr"/>
       <c r="P273" t="inlineStr"/>
       <c r="Q273" t="inlineStr"/>
+      <c r="R273" s="2" t="n">
+        <v>37742</v>
+      </c>
     </row>
     <row r="274">
       <c r="A274" t="n">
@@ -12253,6 +13078,9 @@
       <c r="O274" t="inlineStr"/>
       <c r="P274" t="inlineStr"/>
       <c r="Q274" t="inlineStr"/>
+      <c r="R274" s="2" t="n">
+        <v>37712</v>
+      </c>
     </row>
     <row r="275">
       <c r="A275" t="n">
@@ -12296,6 +13124,9 @@
       <c r="O275" t="inlineStr"/>
       <c r="P275" t="inlineStr"/>
       <c r="Q275" t="inlineStr"/>
+      <c r="R275" s="2" t="n">
+        <v>37681</v>
+      </c>
     </row>
     <row r="276">
       <c r="A276" t="n">
@@ -12339,6 +13170,9 @@
       <c r="O276" t="inlineStr"/>
       <c r="P276" t="inlineStr"/>
       <c r="Q276" t="inlineStr"/>
+      <c r="R276" s="2" t="n">
+        <v>37653</v>
+      </c>
     </row>
     <row r="277">
       <c r="A277" t="n">
@@ -12382,6 +13216,9 @@
       <c r="O277" t="inlineStr"/>
       <c r="P277" t="inlineStr"/>
       <c r="Q277" t="inlineStr"/>
+      <c r="R277" s="2" t="n">
+        <v>37622</v>
+      </c>
     </row>
     <row r="278">
       <c r="A278" t="n">
@@ -12425,6 +13262,9 @@
       <c r="Q278" t="n">
         <v>0.6899999999999999</v>
       </c>
+      <c r="R278" s="2" t="n">
+        <v>44287</v>
+      </c>
     </row>
     <row r="279">
       <c r="A279" t="n">
@@ -12468,6 +13308,9 @@
       <c r="Q279" t="n">
         <v>0.6899999999999999</v>
       </c>
+      <c r="R279" s="2" t="n">
+        <v>44256</v>
+      </c>
     </row>
     <row r="280">
       <c r="A280" t="n">
@@ -12511,6 +13354,9 @@
       <c r="Q280" t="n">
         <v>0.7</v>
       </c>
+      <c r="R280" s="2" t="n">
+        <v>44228</v>
+      </c>
     </row>
     <row r="281">
       <c r="A281" t="n">
@@ -12554,6 +13400,9 @@
       <c r="Q281" t="n">
         <v>0.71</v>
       </c>
+      <c r="R281" s="2" t="n">
+        <v>44197</v>
+      </c>
     </row>
     <row r="282">
       <c r="A282" t="n">
@@ -12597,6 +13446,9 @@
       <c r="Q282" t="n">
         <v>0.68</v>
       </c>
+      <c r="R282" s="2" t="n">
+        <v>44075</v>
+      </c>
     </row>
     <row r="283">
       <c r="A283" t="n">
@@ -12640,6 +13492,9 @@
       <c r="Q283" t="n">
         <v>0.66</v>
       </c>
+      <c r="R283" s="2" t="n">
+        <v>44044</v>
+      </c>
     </row>
     <row r="284">
       <c r="A284" t="n">
@@ -12683,6 +13538,9 @@
       <c r="Q284" t="n">
         <v>0.53</v>
       </c>
+      <c r="R284" s="2" t="n">
+        <v>44013</v>
+      </c>
     </row>
     <row r="285">
       <c r="A285" t="n">
@@ -12726,6 +13584,9 @@
       <c r="Q285" t="n">
         <v>0.53</v>
       </c>
+      <c r="R285" s="2" t="n">
+        <v>43983</v>
+      </c>
     </row>
     <row r="286">
       <c r="A286" t="n">
@@ -12769,6 +13630,9 @@
       <c r="Q286" t="n">
         <v>0.51</v>
       </c>
+      <c r="R286" s="2" t="n">
+        <v>43952</v>
+      </c>
     </row>
     <row r="287">
       <c r="A287" t="n">
@@ -12812,6 +13676,9 @@
       <c r="Q287" t="n">
         <v>0.51</v>
       </c>
+      <c r="R287" s="2" t="n">
+        <v>43922</v>
+      </c>
     </row>
     <row r="288">
       <c r="A288" t="n">
@@ -12855,6 +13722,9 @@
       <c r="Q288" t="n">
         <v>0.52</v>
       </c>
+      <c r="R288" s="2" t="n">
+        <v>43891</v>
+      </c>
     </row>
     <row r="289">
       <c r="A289" t="n">
@@ -12898,6 +13768,9 @@
       <c r="Q289" t="n">
         <v>0.5</v>
       </c>
+      <c r="R289" s="2" t="n">
+        <v>43862</v>
+      </c>
     </row>
     <row r="290">
       <c r="A290" t="n">
@@ -12941,6 +13814,9 @@
       <c r="Q290" t="n">
         <v>0.7</v>
       </c>
+      <c r="R290" s="2" t="n">
+        <v>44166</v>
+      </c>
     </row>
     <row r="291">
       <c r="A291" t="n">
@@ -12984,6 +13860,9 @@
       <c r="Q291" t="n">
         <v>0.68</v>
       </c>
+      <c r="R291" s="2" t="n">
+        <v>44136</v>
+      </c>
     </row>
     <row r="292">
       <c r="A292" t="n">
@@ -13027,6 +13906,9 @@
       <c r="Q292" t="n">
         <v>0.68</v>
       </c>
+      <c r="R292" s="2" t="n">
+        <v>44105</v>
+      </c>
     </row>
     <row r="293">
       <c r="A293" t="n">
@@ -13070,6 +13952,9 @@
       <c r="Q293" t="n">
         <v>0.52</v>
       </c>
+      <c r="R293" s="2" t="n">
+        <v>43831</v>
+      </c>
     </row>
     <row r="294">
       <c r="A294" t="n">
@@ -13113,6 +13998,9 @@
       <c r="Q294" t="n">
         <v>0.51</v>
       </c>
+      <c r="R294" s="2" t="n">
+        <v>43709</v>
+      </c>
     </row>
     <row r="295">
       <c r="A295" t="n">
@@ -13156,6 +14044,9 @@
       <c r="Q295" t="n">
         <v>0.52</v>
       </c>
+      <c r="R295" s="2" t="n">
+        <v>43678</v>
+      </c>
     </row>
     <row r="296">
       <c r="A296" t="n">
@@ -13199,6 +14090,9 @@
       <c r="Q296" t="n">
         <v>0.53</v>
       </c>
+      <c r="R296" s="2" t="n">
+        <v>43647</v>
+      </c>
     </row>
     <row r="297">
       <c r="A297" t="n">
@@ -13242,6 +14136,9 @@
       <c r="Q297" t="n">
         <v>0.53</v>
       </c>
+      <c r="R297" s="2" t="n">
+        <v>43617</v>
+      </c>
     </row>
     <row r="298">
       <c r="A298" t="n">
@@ -13285,6 +14182,9 @@
       <c r="Q298" t="n">
         <v>0.52</v>
       </c>
+      <c r="R298" s="2" t="n">
+        <v>43586</v>
+      </c>
     </row>
     <row r="299">
       <c r="A299" t="n">
@@ -13328,6 +14228,9 @@
       <c r="Q299" t="n">
         <v>0.53</v>
       </c>
+      <c r="R299" s="2" t="n">
+        <v>43556</v>
+      </c>
     </row>
     <row r="300">
       <c r="A300" t="n">
@@ -13371,6 +14274,9 @@
       <c r="Q300" t="n">
         <v>0.53</v>
       </c>
+      <c r="R300" s="2" t="n">
+        <v>43525</v>
+      </c>
     </row>
     <row r="301">
       <c r="A301" t="n">
@@ -13414,6 +14320,9 @@
       <c r="Q301" t="n">
         <v>0.53</v>
       </c>
+      <c r="R301" s="2" t="n">
+        <v>43497</v>
+      </c>
     </row>
     <row r="302">
       <c r="A302" t="n">
@@ -13457,6 +14366,9 @@
       <c r="Q302" t="n">
         <v>0.52</v>
       </c>
+      <c r="R302" s="2" t="n">
+        <v>43800</v>
+      </c>
     </row>
     <row r="303">
       <c r="A303" t="n">
@@ -13500,6 +14412,9 @@
       <c r="Q303" t="n">
         <v>0.52</v>
       </c>
+      <c r="R303" s="2" t="n">
+        <v>43770</v>
+      </c>
     </row>
     <row r="304">
       <c r="A304" t="n">
@@ -13543,6 +14458,9 @@
       <c r="Q304" t="n">
         <v>0.52</v>
       </c>
+      <c r="R304" s="2" t="n">
+        <v>43739</v>
+      </c>
     </row>
     <row r="305">
       <c r="A305" t="n">
@@ -13586,6 +14504,9 @@
       <c r="Q305" t="n">
         <v>0.53</v>
       </c>
+      <c r="R305" s="2" t="n">
+        <v>43466</v>
+      </c>
     </row>
     <row r="306">
       <c r="A306" t="n">
@@ -13629,6 +14550,9 @@
       <c r="Q306" t="n">
         <v>0.54</v>
       </c>
+      <c r="R306" s="2" t="n">
+        <v>43344</v>
+      </c>
     </row>
     <row r="307">
       <c r="A307" t="n">
@@ -13672,6 +14596,9 @@
       <c r="Q307" t="n">
         <v>0.54</v>
       </c>
+      <c r="R307" s="2" t="n">
+        <v>43313</v>
+      </c>
     </row>
     <row r="308">
       <c r="A308" t="n">
@@ -13715,6 +14642,9 @@
       <c r="Q308" t="n">
         <v>0.54</v>
       </c>
+      <c r="R308" s="2" t="n">
+        <v>43282</v>
+      </c>
     </row>
     <row r="309">
       <c r="A309" t="n">
@@ -13758,6 +14688,9 @@
       <c r="Q309" t="n">
         <v>0.54</v>
       </c>
+      <c r="R309" s="2" t="n">
+        <v>43252</v>
+      </c>
     </row>
     <row r="310">
       <c r="A310" t="n">
@@ -13801,6 +14734,9 @@
       <c r="Q310" t="n">
         <v>0.55</v>
       </c>
+      <c r="R310" s="2" t="n">
+        <v>43221</v>
+      </c>
     </row>
     <row r="311">
       <c r="A311" t="n">
@@ -13844,6 +14780,9 @@
       <c r="Q311" t="n">
         <v>0.57</v>
       </c>
+      <c r="R311" s="2" t="n">
+        <v>43191</v>
+      </c>
     </row>
     <row r="312">
       <c r="A312" t="n">
@@ -13887,6 +14826,9 @@
       <c r="Q312" t="n">
         <v>0.57</v>
       </c>
+      <c r="R312" s="2" t="n">
+        <v>43160</v>
+      </c>
     </row>
     <row r="313">
       <c r="A313" t="n">
@@ -13930,6 +14872,9 @@
       <c r="Q313" t="n">
         <v>0.58</v>
       </c>
+      <c r="R313" s="2" t="n">
+        <v>43132</v>
+      </c>
     </row>
     <row r="314">
       <c r="A314" t="n">
@@ -13973,6 +14918,9 @@
       <c r="Q314" t="n">
         <v>0.53</v>
       </c>
+      <c r="R314" s="2" t="n">
+        <v>43435</v>
+      </c>
     </row>
     <row r="315">
       <c r="A315" t="n">
@@ -14016,6 +14964,9 @@
       <c r="Q315" t="n">
         <v>0.53</v>
       </c>
+      <c r="R315" s="2" t="n">
+        <v>43405</v>
+      </c>
     </row>
     <row r="316">
       <c r="A316" t="n">
@@ -14059,6 +15010,9 @@
       <c r="Q316" t="n">
         <v>0.54</v>
       </c>
+      <c r="R316" s="2" t="n">
+        <v>43374</v>
+      </c>
     </row>
     <row r="317">
       <c r="A317" t="n">
@@ -14102,6 +15056,9 @@
       <c r="Q317" t="n">
         <v>0.57</v>
       </c>
+      <c r="R317" s="2" t="n">
+        <v>43101</v>
+      </c>
     </row>
     <row r="318">
       <c r="A318" t="n">
@@ -14145,6 +15102,9 @@
       <c r="Q318" t="n">
         <v>0.5600000000000001</v>
       </c>
+      <c r="R318" s="2" t="n">
+        <v>42979</v>
+      </c>
     </row>
     <row r="319">
       <c r="A319" t="n">
@@ -14188,6 +15148,9 @@
       <c r="Q319" t="n">
         <v>0.55</v>
       </c>
+      <c r="R319" s="2" t="n">
+        <v>42948</v>
+      </c>
     </row>
     <row r="320">
       <c r="A320" t="n">
@@ -14231,6 +15194,9 @@
       <c r="Q320" t="n">
         <v>0.54</v>
       </c>
+      <c r="R320" s="2" t="n">
+        <v>42917</v>
+      </c>
     </row>
     <row r="321">
       <c r="A321" t="n">
@@ -14274,6 +15240,9 @@
       <c r="Q321" t="n">
         <v>0.52</v>
       </c>
+      <c r="R321" s="2" t="n">
+        <v>42887</v>
+      </c>
     </row>
     <row r="322">
       <c r="A322" t="n">
@@ -14317,6 +15286,9 @@
       <c r="Q322" t="n">
         <v>0.51</v>
       </c>
+      <c r="R322" s="2" t="n">
+        <v>42856</v>
+      </c>
     </row>
     <row r="323">
       <c r="A323" t="n">
@@ -14360,6 +15332,9 @@
       <c r="Q323" t="n">
         <v>0.5</v>
       </c>
+      <c r="R323" s="2" t="n">
+        <v>42826</v>
+      </c>
     </row>
     <row r="324">
       <c r="A324" t="n">
@@ -14403,6 +15378,9 @@
       <c r="Q324" t="n">
         <v>0.5</v>
       </c>
+      <c r="R324" s="2" t="n">
+        <v>42795</v>
+      </c>
     </row>
     <row r="325">
       <c r="A325" t="n">
@@ -14446,6 +15424,9 @@
       <c r="Q325" t="n">
         <v>0.5</v>
       </c>
+      <c r="R325" s="2" t="n">
+        <v>42767</v>
+      </c>
     </row>
     <row r="326">
       <c r="A326" t="n">
@@ -14489,6 +15470,9 @@
       <c r="Q326" t="n">
         <v>0.55</v>
       </c>
+      <c r="R326" s="2" t="n">
+        <v>43070</v>
+      </c>
     </row>
     <row r="327">
       <c r="A327" t="n">
@@ -14532,6 +15516,9 @@
       <c r="Q327" t="n">
         <v>0.54</v>
       </c>
+      <c r="R327" s="2" t="n">
+        <v>43040</v>
+      </c>
     </row>
     <row r="328">
       <c r="A328" t="n">
@@ -14575,6 +15562,9 @@
       <c r="Q328" t="n">
         <v>0.55</v>
       </c>
+      <c r="R328" s="2" t="n">
+        <v>43009</v>
+      </c>
     </row>
     <row r="329">
       <c r="A329" t="n">
@@ -14618,6 +15608,9 @@
       <c r="Q329" t="n">
         <v>0.49</v>
       </c>
+      <c r="R329" s="2" t="n">
+        <v>42736</v>
+      </c>
     </row>
     <row r="330">
       <c r="A330" t="n">
@@ -14661,6 +15654,9 @@
       <c r="Q330" t="n">
         <v>0.52</v>
       </c>
+      <c r="R330" s="2" t="n">
+        <v>42614</v>
+      </c>
     </row>
     <row r="331">
       <c r="A331" t="n">
@@ -14704,6 +15700,9 @@
       <c r="Q331" t="n">
         <v>0.53</v>
       </c>
+      <c r="R331" s="2" t="n">
+        <v>42583</v>
+      </c>
     </row>
     <row r="332">
       <c r="A332" t="n">
@@ -14747,6 +15746,9 @@
       <c r="Q332" t="n">
         <v>0.49</v>
       </c>
+      <c r="R332" s="2" t="n">
+        <v>42552</v>
+      </c>
     </row>
     <row r="333">
       <c r="A333" t="n">
@@ -14790,6 +15792,9 @@
       <c r="Q333" t="n">
         <v>0.38</v>
       </c>
+      <c r="R333" s="2" t="n">
+        <v>42522</v>
+      </c>
     </row>
     <row r="334">
       <c r="A334" t="n">
@@ -14833,6 +15838,9 @@
       <c r="Q334" t="n">
         <v>0.34</v>
       </c>
+      <c r="R334" s="2" t="n">
+        <v>42491</v>
+      </c>
     </row>
     <row r="335">
       <c r="A335" t="n">
@@ -14876,6 +15884,9 @@
       <c r="Q335" t="n">
         <v>0.34</v>
       </c>
+      <c r="R335" s="2" t="n">
+        <v>42461</v>
+      </c>
     </row>
     <row r="336">
       <c r="A336" t="n">
@@ -14919,6 +15930,9 @@
       <c r="Q336" t="n">
         <v>0.33</v>
       </c>
+      <c r="R336" s="2" t="n">
+        <v>42430</v>
+      </c>
     </row>
     <row r="337">
       <c r="A337" t="n">
@@ -14962,6 +15976,9 @@
       <c r="Q337" t="n">
         <v>0.33</v>
       </c>
+      <c r="R337" s="2" t="n">
+        <v>42401</v>
+      </c>
     </row>
     <row r="338">
       <c r="A338" t="n">
@@ -15005,6 +16022,9 @@
       <c r="Q338" t="n">
         <v>0.47</v>
       </c>
+      <c r="R338" s="2" t="n">
+        <v>42705</v>
+      </c>
     </row>
     <row r="339">
       <c r="A339" t="n">
@@ -15048,6 +16068,9 @@
       <c r="Q339" t="n">
         <v>0.5</v>
       </c>
+      <c r="R339" s="2" t="n">
+        <v>42675</v>
+      </c>
     </row>
     <row r="340">
       <c r="A340" t="n">
@@ -15091,6 +16114,9 @@
       <c r="Q340" t="n">
         <v>0.51</v>
       </c>
+      <c r="R340" s="2" t="n">
+        <v>42644</v>
+      </c>
     </row>
     <row r="341">
       <c r="A341" t="n">
@@ -15134,6 +16160,9 @@
       <c r="Q341" t="n">
         <v>0.33</v>
       </c>
+      <c r="R341" s="2" t="n">
+        <v>42370</v>
+      </c>
     </row>
     <row r="342">
       <c r="A342" t="n">
@@ -15177,6 +16206,9 @@
       <c r="Q342" t="n">
         <v>0.34</v>
       </c>
+      <c r="R342" s="2" t="n">
+        <v>42248</v>
+      </c>
     </row>
     <row r="343">
       <c r="A343" t="n">
@@ -15220,6 +16252,9 @@
       <c r="Q343" t="n">
         <v>0.33</v>
       </c>
+      <c r="R343" s="2" t="n">
+        <v>42217</v>
+      </c>
     </row>
     <row r="344">
       <c r="A344" t="n">
@@ -15263,6 +16298,9 @@
       <c r="Q344" t="n">
         <v>0.33</v>
       </c>
+      <c r="R344" s="2" t="n">
+        <v>42186</v>
+      </c>
     </row>
     <row r="345">
       <c r="A345" t="n">
@@ -15306,6 +16344,9 @@
       <c r="Q345" t="n">
         <v>0.34</v>
       </c>
+      <c r="R345" s="2" t="n">
+        <v>42156</v>
+      </c>
     </row>
     <row r="346">
       <c r="A346" t="n">
@@ -15349,6 +16390,9 @@
       <c r="Q346" t="n">
         <v>0.34</v>
       </c>
+      <c r="R346" s="2" t="n">
+        <v>42125</v>
+      </c>
     </row>
     <row r="347">
       <c r="A347" t="n">
@@ -15392,6 +16436,9 @@
       <c r="Q347" t="n">
         <v>0.32</v>
       </c>
+      <c r="R347" s="2" t="n">
+        <v>42095</v>
+      </c>
     </row>
     <row r="348">
       <c r="A348" t="n">
@@ -15435,6 +16482,9 @@
       <c r="Q348" t="n">
         <v>0.32</v>
       </c>
+      <c r="R348" s="2" t="n">
+        <v>42064</v>
+      </c>
     </row>
     <row r="349">
       <c r="A349" t="n">
@@ -15478,6 +16528,9 @@
       <c r="Q349" t="n">
         <v>0.31</v>
       </c>
+      <c r="R349" s="2" t="n">
+        <v>42036</v>
+      </c>
     </row>
     <row r="350">
       <c r="A350" t="n">
@@ -15521,6 +16574,9 @@
       <c r="Q350" t="n">
         <v>0.32</v>
       </c>
+      <c r="R350" s="2" t="n">
+        <v>42339</v>
+      </c>
     </row>
     <row r="351">
       <c r="A351" t="n">
@@ -15564,6 +16620,9 @@
       <c r="Q351" t="n">
         <v>0.32</v>
       </c>
+      <c r="R351" s="2" t="n">
+        <v>42309</v>
+      </c>
     </row>
     <row r="352">
       <c r="A352" t="n">
@@ -15607,6 +16666,9 @@
       <c r="Q352" t="n">
         <v>0.34</v>
       </c>
+      <c r="R352" s="2" t="n">
+        <v>42278</v>
+      </c>
     </row>
     <row r="353">
       <c r="A353" t="n">
@@ -15650,6 +16712,9 @@
       <c r="Q353" t="n">
         <v>0.3</v>
       </c>
+      <c r="R353" s="2" t="n">
+        <v>42005</v>
+      </c>
     </row>
     <row r="354">
       <c r="A354" t="n">
@@ -15693,6 +16758,9 @@
       <c r="Q354" t="n">
         <v>0.31</v>
       </c>
+      <c r="R354" s="2" t="n">
+        <v>41883</v>
+      </c>
     </row>
     <row r="355">
       <c r="A355" t="n">
@@ -15736,6 +16804,9 @@
       <c r="Q355" t="n">
         <v>0.32</v>
       </c>
+      <c r="R355" s="2" t="n">
+        <v>41852</v>
+      </c>
     </row>
     <row r="356">
       <c r="A356" t="n">
@@ -15779,6 +16850,9 @@
       <c r="Q356" t="n">
         <v>0.32</v>
       </c>
+      <c r="R356" s="2" t="n">
+        <v>41821</v>
+      </c>
     </row>
     <row r="357">
       <c r="A357" t="n">
@@ -15822,6 +16896,9 @@
       <c r="Q357" t="n">
         <v>0.32</v>
       </c>
+      <c r="R357" s="2" t="n">
+        <v>41791</v>
+      </c>
     </row>
     <row r="358">
       <c r="A358" t="n">
@@ -15865,6 +16942,9 @@
       <c r="Q358" t="n">
         <v>0.33</v>
       </c>
+      <c r="R358" s="2" t="n">
+        <v>41760</v>
+      </c>
     </row>
     <row r="359">
       <c r="A359" t="n">
@@ -15908,6 +16988,9 @@
       <c r="Q359" t="n">
         <v>0.33</v>
       </c>
+      <c r="R359" s="2" t="n">
+        <v>41730</v>
+      </c>
     </row>
     <row r="360">
       <c r="A360" t="n">
@@ -15951,6 +17034,9 @@
       <c r="Q360" t="n">
         <v>0.33</v>
       </c>
+      <c r="R360" s="2" t="n">
+        <v>41699</v>
+      </c>
     </row>
     <row r="361">
       <c r="A361" t="n">
@@ -15994,6 +17080,9 @@
       <c r="Q361" t="n">
         <v>0.32</v>
       </c>
+      <c r="R361" s="2" t="n">
+        <v>41671</v>
+      </c>
     </row>
     <row r="362">
       <c r="A362" t="n">
@@ -16037,6 +17126,9 @@
       <c r="Q362" t="n">
         <v>0.32</v>
       </c>
+      <c r="R362" s="2" t="n">
+        <v>41974</v>
+      </c>
     </row>
     <row r="363">
       <c r="A363" t="n">
@@ -16080,6 +17172,9 @@
       <c r="Q363" t="n">
         <v>0.3</v>
       </c>
+      <c r="R363" s="2" t="n">
+        <v>41944</v>
+      </c>
     </row>
     <row r="364">
       <c r="A364" t="n">
@@ -16123,6 +17218,9 @@
       <c r="Q364" t="n">
         <v>0.3</v>
       </c>
+      <c r="R364" s="2" t="n">
+        <v>41913</v>
+      </c>
     </row>
     <row r="365">
       <c r="A365" t="n">
@@ -16166,6 +17264,9 @@
       <c r="Q365" t="n">
         <v>0.32</v>
       </c>
+      <c r="R365" s="2" t="n">
+        <v>41640</v>
+      </c>
     </row>
     <row r="366">
       <c r="A366" t="n">
@@ -16209,6 +17310,9 @@
       <c r="Q366" t="n">
         <v>0.32</v>
       </c>
+      <c r="R366" s="2" t="n">
+        <v>41518</v>
+      </c>
     </row>
     <row r="367">
       <c r="A367" t="n">
@@ -16252,6 +17356,9 @@
       <c r="Q367" t="n">
         <v>0.31</v>
       </c>
+      <c r="R367" s="2" t="n">
+        <v>41487</v>
+      </c>
     </row>
     <row r="368">
       <c r="A368" t="n">
@@ -16295,6 +17402,9 @@
       <c r="Q368" t="n">
         <v>0.3</v>
       </c>
+      <c r="R368" s="2" t="n">
+        <v>41456</v>
+      </c>
     </row>
     <row r="369">
       <c r="A369" t="n">
@@ -16338,6 +17448,9 @@
       <c r="Q369" t="n">
         <v>0.31</v>
       </c>
+      <c r="R369" s="2" t="n">
+        <v>41426</v>
+      </c>
     </row>
     <row r="370">
       <c r="A370" t="n">
@@ -16381,6 +17494,9 @@
       <c r="Q370" t="n">
         <v>0.31</v>
       </c>
+      <c r="R370" s="2" t="n">
+        <v>41395</v>
+      </c>
     </row>
     <row r="371">
       <c r="A371" t="n">
@@ -16424,6 +17540,9 @@
       <c r="Q371" t="n">
         <v>0.31</v>
       </c>
+      <c r="R371" s="2" t="n">
+        <v>41365</v>
+      </c>
     </row>
     <row r="372">
       <c r="A372" t="n">
@@ -16467,6 +17586,9 @@
       <c r="Q372" t="n">
         <v>0.31</v>
       </c>
+      <c r="R372" s="2" t="n">
+        <v>41334</v>
+      </c>
     </row>
     <row r="373">
       <c r="A373" t="n">
@@ -16510,6 +17632,9 @@
       <c r="Q373" t="n">
         <v>0.32</v>
       </c>
+      <c r="R373" s="2" t="n">
+        <v>41306</v>
+      </c>
     </row>
     <row r="374">
       <c r="A374" t="n">
@@ -16553,6 +17678,9 @@
       <c r="Q374" t="n">
         <v>0.32</v>
       </c>
+      <c r="R374" s="2" t="n">
+        <v>41609</v>
+      </c>
     </row>
     <row r="375">
       <c r="A375" t="n">
@@ -16596,6 +17724,9 @@
       <c r="Q375" t="n">
         <v>0.32</v>
       </c>
+      <c r="R375" s="2" t="n">
+        <v>41579</v>
+      </c>
     </row>
     <row r="376">
       <c r="A376" t="n">
@@ -16639,6 +17770,9 @@
       <c r="Q376" t="n">
         <v>0.32</v>
       </c>
+      <c r="R376" s="2" t="n">
+        <v>41548</v>
+      </c>
     </row>
     <row r="377">
       <c r="A377" t="n">
@@ -16682,6 +17816,9 @@
       <c r="Q377" t="n">
         <v>0.31</v>
       </c>
+      <c r="R377" s="2" t="n">
+        <v>41275</v>
+      </c>
     </row>
     <row r="378">
       <c r="A378" t="n">
@@ -16725,6 +17862,9 @@
       <c r="Q378" t="n">
         <v>0.3</v>
       </c>
+      <c r="R378" s="2" t="n">
+        <v>41153</v>
+      </c>
     </row>
     <row r="379">
       <c r="A379" t="n">
@@ -16768,6 +17908,9 @@
       <c r="Q379" t="n">
         <v>0.29</v>
       </c>
+      <c r="R379" s="2" t="n">
+        <v>41122</v>
+      </c>
     </row>
     <row r="380">
       <c r="A380" t="n">
@@ -16811,6 +17954,9 @@
       <c r="Q380" t="n">
         <v>0.29</v>
       </c>
+      <c r="R380" s="2" t="n">
+        <v>41091</v>
+      </c>
     </row>
     <row r="381">
       <c r="A381" t="n">
@@ -16854,6 +18000,9 @@
       <c r="Q381" t="n">
         <v>0.3</v>
       </c>
+      <c r="R381" s="2" t="n">
+        <v>41061</v>
+      </c>
     </row>
     <row r="382">
       <c r="A382" t="n">
@@ -16897,6 +18046,9 @@
       <c r="Q382" t="n">
         <v>0.3</v>
       </c>
+      <c r="R382" s="2" t="n">
+        <v>41030</v>
+      </c>
     </row>
     <row r="383">
       <c r="A383" t="n">
@@ -16940,6 +18092,9 @@
       <c r="Q383" t="n">
         <v>0.31</v>
       </c>
+      <c r="R383" s="2" t="n">
+        <v>41000</v>
+      </c>
     </row>
     <row r="384">
       <c r="A384" t="n">
@@ -16983,6 +18138,9 @@
       <c r="Q384" t="n">
         <v>0.31</v>
       </c>
+      <c r="R384" s="2" t="n">
+        <v>40969</v>
+      </c>
     </row>
     <row r="385">
       <c r="A385" t="n">
@@ -17026,6 +18184,9 @@
       <c r="Q385" t="n">
         <v>0.31</v>
       </c>
+      <c r="R385" s="2" t="n">
+        <v>40940</v>
+      </c>
     </row>
     <row r="386">
       <c r="A386" t="n">
@@ -17069,6 +18230,9 @@
       <c r="Q386" t="n">
         <v>0.31</v>
       </c>
+      <c r="R386" s="2" t="n">
+        <v>41244</v>
+      </c>
     </row>
     <row r="387">
       <c r="A387" t="n">
@@ -17112,6 +18276,9 @@
       <c r="Q387" t="n">
         <v>0.3</v>
       </c>
+      <c r="R387" s="2" t="n">
+        <v>41214</v>
+      </c>
     </row>
     <row r="388">
       <c r="A388" t="n">
@@ -17155,6 +18322,9 @@
       <c r="Q388" t="n">
         <v>0.31</v>
       </c>
+      <c r="R388" s="2" t="n">
+        <v>41183</v>
+      </c>
     </row>
     <row r="389">
       <c r="A389" t="n">
@@ -17198,6 +18368,9 @@
       <c r="Q389" t="n">
         <v>0.31</v>
       </c>
+      <c r="R389" s="2" t="n">
+        <v>40909</v>
+      </c>
     </row>
     <row r="390">
       <c r="A390" t="n">
@@ -17241,6 +18414,9 @@
       <c r="Q390" t="n">
         <v>0.32</v>
       </c>
+      <c r="R390" s="2" t="n">
+        <v>40787</v>
+      </c>
     </row>
     <row r="391">
       <c r="A391" t="n">
@@ -17284,6 +18460,9 @@
       <c r="Q391" t="n">
         <v>0.33</v>
       </c>
+      <c r="R391" s="2" t="n">
+        <v>40756</v>
+      </c>
     </row>
     <row r="392">
       <c r="A392" t="n">
@@ -17327,6 +18506,9 @@
       <c r="Q392" t="n">
         <v>0.33</v>
       </c>
+      <c r="R392" s="2" t="n">
+        <v>40725</v>
+      </c>
     </row>
     <row r="393">
       <c r="A393" t="n">
@@ -17370,6 +18552,9 @@
       <c r="Q393" t="n">
         <v>0.34</v>
       </c>
+      <c r="R393" s="2" t="n">
+        <v>40695</v>
+      </c>
     </row>
     <row r="394">
       <c r="A394" t="n">
@@ -17413,6 +18598,9 @@
       <c r="Q394" t="n">
         <v>0.33</v>
       </c>
+      <c r="R394" s="2" t="n">
+        <v>40664</v>
+      </c>
     </row>
     <row r="395">
       <c r="A395" t="n">
@@ -17456,6 +18644,9 @@
       <c r="Q395" t="n">
         <v>0.33</v>
       </c>
+      <c r="R395" s="2" t="n">
+        <v>40634</v>
+      </c>
     </row>
     <row r="396">
       <c r="A396" t="n">
@@ -17499,6 +18690,9 @@
       <c r="Q396" t="n">
         <v>0.32</v>
       </c>
+      <c r="R396" s="2" t="n">
+        <v>40603</v>
+      </c>
     </row>
     <row r="397">
       <c r="A397" t="n">
@@ -17542,6 +18736,9 @@
       <c r="Q397" t="n">
         <v>0.31</v>
       </c>
+      <c r="R397" s="2" t="n">
+        <v>40575</v>
+      </c>
     </row>
     <row r="398">
       <c r="A398" t="n">
@@ -17585,6 +18782,9 @@
       <c r="Q398" t="n">
         <v>0.31</v>
       </c>
+      <c r="R398" s="2" t="n">
+        <v>40878</v>
+      </c>
     </row>
     <row r="399">
       <c r="A399" t="n">
@@ -17628,6 +18828,9 @@
       <c r="Q399" t="n">
         <v>0.32</v>
       </c>
+      <c r="R399" s="2" t="n">
+        <v>40848</v>
+      </c>
     </row>
     <row r="400">
       <c r="A400" t="n">
@@ -17671,6 +18874,9 @@
       <c r="Q400" t="n">
         <v>0.32</v>
       </c>
+      <c r="R400" s="2" t="n">
+        <v>40817</v>
+      </c>
     </row>
     <row r="401">
       <c r="A401" t="n">
@@ -17714,6 +18920,9 @@
       <c r="Q401" t="n">
         <v>0.3</v>
       </c>
+      <c r="R401" s="2" t="n">
+        <v>40544</v>
+      </c>
     </row>
     <row r="402">
       <c r="A402" t="n">
@@ -17757,6 +18966,9 @@
       <c r="Q402" t="n">
         <v>0.3</v>
       </c>
+      <c r="R402" s="2" t="n">
+        <v>40422</v>
+      </c>
     </row>
     <row r="403">
       <c r="A403" t="n">
@@ -17800,6 +19012,9 @@
       <c r="Q403" t="n">
         <v>0.29</v>
       </c>
+      <c r="R403" s="2" t="n">
+        <v>40391</v>
+      </c>
     </row>
     <row r="404">
       <c r="A404" t="n">
@@ -17843,6 +19058,9 @@
       <c r="Q404" t="n">
         <v>0.29</v>
       </c>
+      <c r="R404" s="2" t="n">
+        <v>40360</v>
+      </c>
     </row>
     <row r="405">
       <c r="A405" t="n">
@@ -17886,6 +19104,9 @@
       <c r="Q405" t="n">
         <v>0.28</v>
       </c>
+      <c r="R405" s="2" t="n">
+        <v>40330</v>
+      </c>
     </row>
     <row r="406">
       <c r="A406" t="n">
@@ -17929,6 +19150,9 @@
       <c r="Q406" t="n">
         <v>0.28</v>
       </c>
+      <c r="R406" s="2" t="n">
+        <v>40299</v>
+      </c>
     </row>
     <row r="407">
       <c r="A407" t="n">
@@ -17972,6 +19196,9 @@
       <c r="Q407" t="n">
         <v>0.28</v>
       </c>
+      <c r="R407" s="2" t="n">
+        <v>40269</v>
+      </c>
     </row>
     <row r="408">
       <c r="A408" t="n">
@@ -18015,6 +19242,9 @@
       <c r="Q408" t="n">
         <v>0.31</v>
       </c>
+      <c r="R408" s="2" t="n">
+        <v>40238</v>
+      </c>
     </row>
     <row r="409">
       <c r="A409" t="n">
@@ -18058,6 +19288,9 @@
       <c r="Q409" t="n">
         <v>0.31</v>
       </c>
+      <c r="R409" s="2" t="n">
+        <v>40210</v>
+      </c>
     </row>
     <row r="410">
       <c r="A410" t="n">
@@ -18101,6 +19334,9 @@
       <c r="Q410" t="n">
         <v>0.3</v>
       </c>
+      <c r="R410" s="2" t="n">
+        <v>40513</v>
+      </c>
     </row>
     <row r="411">
       <c r="A411" t="n">
@@ -18144,6 +19380,9 @@
       <c r="Q411" t="n">
         <v>0.31</v>
       </c>
+      <c r="R411" s="2" t="n">
+        <v>40483</v>
+      </c>
     </row>
     <row r="412">
       <c r="A412" t="n">
@@ -18187,6 +19426,9 @@
       <c r="Q412" t="n">
         <v>0.32</v>
       </c>
+      <c r="R412" s="2" t="n">
+        <v>40452</v>
+      </c>
     </row>
     <row r="413">
       <c r="A413" t="n">
@@ -18230,6 +19472,9 @@
       <c r="Q413" t="n">
         <v>0.32</v>
       </c>
+      <c r="R413" s="2" t="n">
+        <v>40179</v>
+      </c>
     </row>
     <row r="414">
       <c r="A414" t="n">
@@ -18273,6 +19518,9 @@
       <c r="Q414" t="n">
         <v>0.33</v>
       </c>
+      <c r="R414" s="2" t="n">
+        <v>40057</v>
+      </c>
     </row>
     <row r="415">
       <c r="A415" t="n">
@@ -18316,6 +19564,9 @@
       <c r="Q415" t="n">
         <v>0.36</v>
       </c>
+      <c r="R415" s="2" t="n">
+        <v>40026</v>
+      </c>
     </row>
     <row r="416">
       <c r="A416" t="n">
@@ -18359,6 +19610,9 @@
       <c r="Q416" t="n">
         <v>0.32</v>
       </c>
+      <c r="R416" s="2" t="n">
+        <v>39995</v>
+      </c>
     </row>
     <row r="417">
       <c r="A417" t="n">
@@ -18402,6 +19656,9 @@
       <c r="Q417" t="n">
         <v>0.31</v>
       </c>
+      <c r="R417" s="2" t="n">
+        <v>39965</v>
+      </c>
     </row>
     <row r="418">
       <c r="A418" t="n">
@@ -18445,6 +19702,9 @@
       <c r="Q418" t="n">
         <v>0.3</v>
       </c>
+      <c r="R418" s="2" t="n">
+        <v>39934</v>
+      </c>
     </row>
     <row r="419">
       <c r="A419" t="n">
@@ -18488,6 +19748,9 @@
       <c r="Q419" t="n">
         <v>0.29</v>
       </c>
+      <c r="R419" s="2" t="n">
+        <v>39904</v>
+      </c>
     </row>
     <row r="420">
       <c r="A420" t="n">
@@ -18531,6 +19794,9 @@
       <c r="Q420" t="n">
         <v>0.29</v>
       </c>
+      <c r="R420" s="2" t="n">
+        <v>39873</v>
+      </c>
     </row>
     <row r="421">
       <c r="A421" t="n">
@@ -18574,6 +19840,9 @@
       <c r="Q421" t="n">
         <v>0.28</v>
       </c>
+      <c r="R421" s="2" t="n">
+        <v>39845</v>
+      </c>
     </row>
     <row r="422">
       <c r="A422" t="n">
@@ -18617,6 +19886,9 @@
       <c r="Q422" t="n">
         <v>0.33</v>
       </c>
+      <c r="R422" s="2" t="n">
+        <v>40148</v>
+      </c>
     </row>
     <row r="423">
       <c r="A423" t="n">
@@ -18660,6 +19932,9 @@
       <c r="Q423" t="n">
         <v>0.34</v>
       </c>
+      <c r="R423" s="2" t="n">
+        <v>40118</v>
+      </c>
     </row>
     <row r="424">
       <c r="A424" t="n">
@@ -18703,6 +19978,9 @@
       <c r="Q424" t="n">
         <v>0.33</v>
       </c>
+      <c r="R424" s="2" t="n">
+        <v>40087</v>
+      </c>
     </row>
     <row r="425">
       <c r="A425" t="n">
@@ -18746,6 +20024,9 @@
       <c r="Q425" t="n">
         <v>0.29</v>
       </c>
+      <c r="R425" s="2" t="n">
+        <v>39814</v>
+      </c>
     </row>
     <row r="426">
       <c r="A426" t="n">
@@ -18789,6 +20070,9 @@
       <c r="Q426" t="n">
         <v>0.26</v>
       </c>
+      <c r="R426" s="2" t="n">
+        <v>39692</v>
+      </c>
     </row>
     <row r="427">
       <c r="A427" t="n">
@@ -18832,6 +20116,9 @@
       <c r="Q427" t="n">
         <v>0.27</v>
       </c>
+      <c r="R427" s="2" t="n">
+        <v>39661</v>
+      </c>
     </row>
     <row r="428">
       <c r="A428" t="n">
@@ -18875,6 +20162,9 @@
       <c r="Q428" t="n">
         <v>0.28</v>
       </c>
+      <c r="R428" s="2" t="n">
+        <v>39630</v>
+      </c>
     </row>
     <row r="429">
       <c r="A429" t="n">
@@ -18918,6 +20208,9 @@
       <c r="Q429" t="n">
         <v>0.27</v>
       </c>
+      <c r="R429" s="2" t="n">
+        <v>39600</v>
+      </c>
     </row>
     <row r="430">
       <c r="A430" t="n">
@@ -18961,6 +20254,9 @@
       <c r="Q430" t="n">
         <v>0.28</v>
       </c>
+      <c r="R430" s="2" t="n">
+        <v>39569</v>
+      </c>
     </row>
     <row r="431">
       <c r="A431" t="n">
@@ -19004,6 +20300,9 @@
       <c r="Q431" t="n">
         <v>0.28</v>
       </c>
+      <c r="R431" s="2" t="n">
+        <v>39539</v>
+      </c>
     </row>
     <row r="432">
       <c r="A432" t="n">
@@ -19047,6 +20346,9 @@
       <c r="Q432" t="n">
         <v>0.27</v>
       </c>
+      <c r="R432" s="2" t="n">
+        <v>39508</v>
+      </c>
     </row>
     <row r="433">
       <c r="A433" t="n">
@@ -19090,6 +20392,9 @@
       <c r="Q433" t="n">
         <v>0.26</v>
       </c>
+      <c r="R433" s="2" t="n">
+        <v>39479</v>
+      </c>
     </row>
     <row r="434">
       <c r="A434" t="n">
@@ -19133,6 +20438,9 @@
       <c r="Q434" t="n">
         <v>0.26</v>
       </c>
+      <c r="R434" s="2" t="n">
+        <v>39783</v>
+      </c>
     </row>
     <row r="435">
       <c r="A435" t="n">
@@ -19176,6 +20484,9 @@
       <c r="Q435" t="n">
         <v>0.23</v>
       </c>
+      <c r="R435" s="2" t="n">
+        <v>39753</v>
+      </c>
     </row>
     <row r="436">
       <c r="A436" t="n">
@@ -19219,6 +20530,9 @@
       <c r="Q436" t="n">
         <v>0.24</v>
       </c>
+      <c r="R436" s="2" t="n">
+        <v>39722</v>
+      </c>
     </row>
     <row r="437">
       <c r="A437" t="n">
@@ -19262,6 +20576,9 @@
       <c r="Q437" t="n">
         <v>0.26</v>
       </c>
+      <c r="R437" s="2" t="n">
+        <v>39448</v>
+      </c>
     </row>
     <row r="438">
       <c r="A438" t="n">
@@ -19305,6 +20622,9 @@
       <c r="Q438" t="n">
         <v>0.26</v>
       </c>
+      <c r="R438" s="2" t="n">
+        <v>39326</v>
+      </c>
     </row>
     <row r="439">
       <c r="A439" t="n">
@@ -19348,6 +20668,9 @@
       <c r="Q439" t="n">
         <v>0.26</v>
       </c>
+      <c r="R439" s="2" t="n">
+        <v>39295</v>
+      </c>
     </row>
     <row r="440">
       <c r="A440" t="n">
@@ -19391,6 +20714,9 @@
       <c r="Q440" t="n">
         <v>0.26</v>
       </c>
+      <c r="R440" s="2" t="n">
+        <v>39264</v>
+      </c>
     </row>
     <row r="441">
       <c r="A441" t="n">
@@ -19434,6 +20760,9 @@
       <c r="Q441" t="n">
         <v>0.26</v>
       </c>
+      <c r="R441" s="2" t="n">
+        <v>39234</v>
+      </c>
     </row>
     <row r="442">
       <c r="A442" t="n">
@@ -19477,6 +20806,9 @@
       <c r="Q442" t="n">
         <v>0.25</v>
       </c>
+      <c r="R442" s="2" t="n">
+        <v>39203</v>
+      </c>
     </row>
     <row r="443">
       <c r="A443" t="n">
@@ -19520,6 +20852,9 @@
       <c r="Q443" t="n">
         <v>0.26</v>
       </c>
+      <c r="R443" s="2" t="n">
+        <v>39173</v>
+      </c>
     </row>
     <row r="444">
       <c r="A444" t="n">
@@ -19563,6 +20898,9 @@
       <c r="Q444" t="n">
         <v>0.25</v>
       </c>
+      <c r="R444" s="2" t="n">
+        <v>39142</v>
+      </c>
     </row>
     <row r="445">
       <c r="A445" t="n">
@@ -19606,6 +20944,9 @@
       <c r="Q445" t="n">
         <v>0.24</v>
       </c>
+      <c r="R445" s="2" t="n">
+        <v>39114</v>
+      </c>
     </row>
     <row r="446">
       <c r="A446" t="n">
@@ -19649,6 +20990,9 @@
       <c r="Q446" t="n">
         <v>0.26</v>
       </c>
+      <c r="R446" s="2" t="n">
+        <v>39417</v>
+      </c>
     </row>
     <row r="447">
       <c r="A447" t="n">
@@ -19692,6 +21036,9 @@
       <c r="Q447" t="n">
         <v>0.26</v>
       </c>
+      <c r="R447" s="2" t="n">
+        <v>39387</v>
+      </c>
     </row>
     <row r="448">
       <c r="A448" t="n">
@@ -19735,6 +21082,9 @@
       <c r="Q448" t="n">
         <v>0.27</v>
       </c>
+      <c r="R448" s="2" t="n">
+        <v>39356</v>
+      </c>
     </row>
     <row r="449">
       <c r="A449" t="n">
@@ -19778,6 +21128,9 @@
       <c r="Q449" t="n">
         <v>0.25</v>
       </c>
+      <c r="R449" s="2" t="n">
+        <v>39083</v>
+      </c>
     </row>
     <row r="450">
       <c r="A450" t="n">
@@ -19821,6 +21174,9 @@
       <c r="Q450" t="n">
         <v>0.25</v>
       </c>
+      <c r="R450" s="2" t="n">
+        <v>38961</v>
+      </c>
     </row>
     <row r="451">
       <c r="A451" t="n">
@@ -19864,6 +21220,9 @@
       <c r="Q451" t="n">
         <v>0.25</v>
       </c>
+      <c r="R451" s="2" t="n">
+        <v>38930</v>
+      </c>
     </row>
     <row r="452">
       <c r="A452" t="n">
@@ -19907,6 +21266,9 @@
       <c r="Q452" t="n">
         <v>0.24</v>
       </c>
+      <c r="R452" s="2" t="n">
+        <v>38899</v>
+      </c>
     </row>
     <row r="453">
       <c r="A453" t="n">
@@ -19950,6 +21312,9 @@
       <c r="Q453" t="n">
         <v>0.24</v>
       </c>
+      <c r="R453" s="2" t="n">
+        <v>38869</v>
+      </c>
     </row>
     <row r="454">
       <c r="A454" t="n">
@@ -19993,6 +21358,9 @@
       <c r="Q454" t="n">
         <v>0.25</v>
       </c>
+      <c r="R454" s="2" t="n">
+        <v>38838</v>
+      </c>
     </row>
     <row r="455">
       <c r="A455" t="n">
@@ -20036,6 +21404,9 @@
       <c r="Q455" t="n">
         <v>0.24</v>
       </c>
+      <c r="R455" s="2" t="n">
+        <v>38808</v>
+      </c>
     </row>
     <row r="456">
       <c r="A456" t="n">
@@ -20079,6 +21450,9 @@
       <c r="Q456" t="n">
         <v>0.23</v>
       </c>
+      <c r="R456" s="2" t="n">
+        <v>38777</v>
+      </c>
     </row>
     <row r="457">
       <c r="A457" t="n">
@@ -20122,6 +21496,9 @@
       <c r="Q457" t="n">
         <v>0.23</v>
       </c>
+      <c r="R457" s="2" t="n">
+        <v>38749</v>
+      </c>
     </row>
     <row r="458">
       <c r="A458" t="n">
@@ -20165,6 +21542,9 @@
       <c r="Q458" t="n">
         <v>0.24</v>
       </c>
+      <c r="R458" s="2" t="n">
+        <v>39052</v>
+      </c>
     </row>
     <row r="459">
       <c r="A459" t="n">
@@ -20208,6 +21588,9 @@
       <c r="Q459" t="n">
         <v>0.25</v>
       </c>
+      <c r="R459" s="2" t="n">
+        <v>39022</v>
+      </c>
     </row>
     <row r="460">
       <c r="A460" t="n">
@@ -20251,6 +21634,9 @@
       <c r="Q460" t="n">
         <v>0.25</v>
       </c>
+      <c r="R460" s="2" t="n">
+        <v>38991</v>
+      </c>
     </row>
     <row r="461">
       <c r="A461" t="n">
@@ -20294,6 +21680,9 @@
       <c r="Q461" t="n">
         <v>0.24</v>
       </c>
+      <c r="R461" s="2" t="n">
+        <v>38718</v>
+      </c>
     </row>
     <row r="462">
       <c r="A462" t="n">
@@ -20337,6 +21726,9 @@
       <c r="Q462" t="n">
         <v>0.24</v>
       </c>
+      <c r="R462" s="2" t="n">
+        <v>38596</v>
+      </c>
     </row>
     <row r="463">
       <c r="A463" t="n">
@@ -20380,6 +21772,9 @@
       <c r="Q463" t="n">
         <v>0.25</v>
       </c>
+      <c r="R463" s="2" t="n">
+        <v>38565</v>
+      </c>
     </row>
     <row r="464">
       <c r="A464" t="n">
@@ -20423,6 +21818,9 @@
       <c r="Q464" t="n">
         <v>0.24</v>
       </c>
+      <c r="R464" s="2" t="n">
+        <v>38534</v>
+      </c>
     </row>
     <row r="465">
       <c r="A465" t="n">
@@ -20466,6 +21864,9 @@
       <c r="Q465" t="n">
         <v>0.25</v>
       </c>
+      <c r="R465" s="2" t="n">
+        <v>38504</v>
+      </c>
     </row>
     <row r="466">
       <c r="A466" t="n">
@@ -20509,6 +21910,9 @@
       <c r="Q466" t="n">
         <v>0.26</v>
       </c>
+      <c r="R466" s="2" t="n">
+        <v>38473</v>
+      </c>
     </row>
     <row r="467">
       <c r="A467" t="n">
@@ -20552,6 +21956,9 @@
       <c r="Q467" t="n">
         <v>0.26</v>
       </c>
+      <c r="R467" s="2" t="n">
+        <v>38443</v>
+      </c>
     </row>
     <row r="468">
       <c r="A468" t="n">
@@ -20595,6 +22002,9 @@
       <c r="Q468" t="n">
         <v>0.27</v>
       </c>
+      <c r="R468" s="2" t="n">
+        <v>38412</v>
+      </c>
     </row>
     <row r="469">
       <c r="A469" t="n">
@@ -20638,6 +22048,9 @@
       <c r="Q469" t="n">
         <v>0.26</v>
       </c>
+      <c r="R469" s="2" t="n">
+        <v>38384</v>
+      </c>
     </row>
     <row r="470">
       <c r="A470" t="n">
@@ -20681,6 +22094,9 @@
       <c r="Q470" t="n">
         <v>0.23</v>
       </c>
+      <c r="R470" s="2" t="n">
+        <v>38687</v>
+      </c>
     </row>
     <row r="471">
       <c r="A471" t="n">
@@ -20724,6 +22140,9 @@
       <c r="Q471" t="n">
         <v>0.23</v>
       </c>
+      <c r="R471" s="2" t="n">
+        <v>38657</v>
+      </c>
     </row>
     <row r="472">
       <c r="A472" t="n">
@@ -20767,6 +22186,9 @@
       <c r="Q472" t="n">
         <v>0.24</v>
       </c>
+      <c r="R472" s="2" t="n">
+        <v>38626</v>
+      </c>
     </row>
     <row r="473">
       <c r="A473" t="n">
@@ -20810,6 +22232,9 @@
       <c r="Q473" t="n">
         <v>0.27</v>
       </c>
+      <c r="R473" s="2" t="n">
+        <v>38353</v>
+      </c>
     </row>
     <row r="474">
       <c r="A474" t="n">
@@ -20853,6 +22278,9 @@
       <c r="Q474" t="n">
         <v>0.25</v>
       </c>
+      <c r="R474" s="2" t="n">
+        <v>38231</v>
+      </c>
     </row>
     <row r="475">
       <c r="A475" t="n">
@@ -20896,6 +22324,9 @@
       <c r="Q475" t="n">
         <v>0.25</v>
       </c>
+      <c r="R475" s="2" t="n">
+        <v>38200</v>
+      </c>
     </row>
     <row r="476">
       <c r="A476" t="n">
@@ -20939,6 +22370,9 @@
       <c r="Q476" t="n">
         <v>0.25</v>
       </c>
+      <c r="R476" s="2" t="n">
+        <v>38169</v>
+      </c>
     </row>
     <row r="477">
       <c r="A477" t="n">
@@ -20982,6 +22416,9 @@
       <c r="Q477" t="n">
         <v>0.24</v>
       </c>
+      <c r="R477" s="2" t="n">
+        <v>38139</v>
+      </c>
     </row>
     <row r="478">
       <c r="A478" t="n">
@@ -21025,6 +22462,9 @@
       <c r="Q478" t="n">
         <v>0.24</v>
       </c>
+      <c r="R478" s="2" t="n">
+        <v>38108</v>
+      </c>
     </row>
     <row r="479">
       <c r="A479" t="n">
@@ -21068,6 +22508,9 @@
       <c r="Q479" t="n">
         <v>0.24</v>
       </c>
+      <c r="R479" s="2" t="n">
+        <v>38078</v>
+      </c>
     </row>
     <row r="480">
       <c r="A480" t="n">
@@ -21111,6 +22554,9 @@
       <c r="Q480" t="n">
         <v>0.25</v>
       </c>
+      <c r="R480" s="2" t="n">
+        <v>38047</v>
+      </c>
     </row>
     <row r="481">
       <c r="A481" t="n">
@@ -21154,6 +22600,9 @@
       <c r="Q481" t="n">
         <v>0.2</v>
       </c>
+      <c r="R481" s="2" t="n">
+        <v>38018</v>
+      </c>
     </row>
     <row r="482">
       <c r="A482" t="n">
@@ -21197,6 +22646,9 @@
       <c r="Q482" t="n">
         <v>0.27</v>
       </c>
+      <c r="R482" s="2" t="n">
+        <v>38322</v>
+      </c>
     </row>
     <row r="483">
       <c r="A483" t="n">
@@ -21240,6 +22692,9 @@
       <c r="Q483" t="n">
         <v>0.26</v>
       </c>
+      <c r="R483" s="2" t="n">
+        <v>38292</v>
+      </c>
     </row>
     <row r="484">
       <c r="A484" t="n">
@@ -21283,6 +22738,9 @@
       <c r="Q484" t="n">
         <v>0.25</v>
       </c>
+      <c r="R484" s="2" t="n">
+        <v>38261</v>
+      </c>
     </row>
     <row r="485">
       <c r="A485" t="n">
@@ -21326,6 +22784,9 @@
       <c r="Q485" t="n">
         <v>0.16</v>
       </c>
+      <c r="R485" s="2" t="n">
+        <v>37987</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
